--- a/docs/style-comparison-final.xlsx
+++ b/docs/style-comparison-final.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,6 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="52" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,11 +518,6 @@
           <t>Which reads better?</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Reviewed: was the loss material?</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -536,20 +530,22 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>5 साल की बेटी के लिए सबसे उपयुक्त सरकारी योजना **सुकन्या समृद्धि योजना (Sukanya Samriddhi Yojana)** है।
-इसके मुख्य लाभ:
-*   **ब्याज दर:** वर्तमान में 8.2 प्रतिशत है, जो अन्य छोटी बचत योजनाओं की तुलना में काफी बेहतर है।
-*   **कर लाभ:** इसमें मिलने वाला ब्याज और परिपक्वता पर मिलने वाली पूरी राशि आयकर के तहत कर-मुक्त (tax-free) होती है।
-*   **अन्य योजनाएँ:** PPF भी एक अच्छा विकल्प हो सकता है, लेकिन बेटी की भविष्य की पढ़ाई और शादी जैसे विशिष्ट लक्ष्यों के लिए SSY सबसे उपयुक्त मानी जाती है।</t>
+          <t>5 साल की बेटी के लिए **सुकन्या समृद्धि योजना (Sukanya Samriddhi Yojana)** सबसे उपयुक्त सरकारी विकल्प है।
+इसका ब्याज दर वर्तमान में **8.2%** है, जो 1 जुलाई 2026 से लागू है। यह दर हर तिमाही में सरकार द्वारा समीक्षा की जाती है, इसलिए भविष्य में बदलाव हो सकता है।
+इस योजना के मुख्य लाभ:
+* बेटी के लिए लंबे समय तक सुरक्षित निवेश।
+* परिपक्वता पर प्राप्त राशि पर आयकर छूट (Section 80C और 80TTB के तहत)।
+कृपया ध्यान दें: यह जानकारी सामान्य शिक्षा के उद्देश्यों से है। किसी भी योजना में निवेश करने से पहले अपने वित्तीय सलाहकार या CA से अपनी स्थिति के अनुसार पुष्टि अवश्य करें।</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>5 साल की बेटी के लिए सबसे उपयुक्त सरकारी योजना **सुकन्या समृद्धि योजना (Sukanya Samriddhi Yojana)** है।
-इसके मुख्य लाभ:
-*   **ब्याज दर:** वर्तमान में 8.2 प्रतिशत है, जो अन्य छोटी बचत योजनाओं की तुलना में काफी बेहतर है।
-*   **कर लाभ:** इसमें मिलने वाला ब्याज और परिपक्वता पर मिलने वाली पूरी राशि आयकर के तहत कर-मुक्त (tax-free) होती है।
-*   **अन्य योजनाएँ:** PPF भी एक अच्छा विकल्प हो सकता है, लेकिन बेटी की भविष्य की पढ़ाई और शादी जैसे विशिष्ट लक्ष्यों के लिए SSY सबसे उपयुक्त मानी जाती है।</t>
+          <t>5 साल की बेटी के लिए **सुकन्या समृद्धि योजना (Sukanya Samriddhi Yojana)** सबसे उपयुक्त सरकारी विकल्प है।
+इसका ब्याज दर वर्तमान में **8.2%** है, जो 1 जुलाई 2026 से लागू है। यह दर हर तिमाही में सरकार द्वारा समीक्षा की जाती है, इसलिए भविष्य में बदलाव हो सकता है।
+इस योजना के मुख्य लाभ:
+* बेटी के लिए लंबे समय तक सुरक्षित निवेश।
+* परिपक्वता पर प्राप्त राशि पर आयकर छूट (Section 80C और 80TTB के तहत)।
+कृपया ध्यान दें: यह जानकारी सामान्य शिक्षा के उद्देश्यों से है। किसी भी योजना में निवेश करने से पहले अपने वित्तीय सलाहकार या CA से अपनी स्थिति के अनुसार पुष्टि अवश्य करें।</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -573,17 +569,12 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>13.7</v>
+        <v>11.6</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14.4</v>
+        <v>12.6</v>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>no loss</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -596,16 +587,14 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>₹1,00,000 की 1 साल की FD मैच्योर होने पर आपको **₹1,06,398.02** मिलेंगे।
-इसमें से ₹6,398.02 ब्याज है। ध्यान रखें कि इस ब्याज पर आपकी आयकर स्लैब के हिसाब से टैक्स लगेगा।
-SBI का यह रेट 15 दिसंबर 2025 से लागू है।</t>
+          <t>1 लाख रुपये की 1 साल की FD मैच्योर होने पर आपको ₹1,06,398.02 मिलेंगे। इसमें ₹6,398.02 ब्याज शामिल है।
+ये रेट SBI के 15 दिसंबर 2025 से लागू हो रहे हैं। ध्यान रखें कि FD पर जो ब्याज मिलता है, वो आपकी आय टैक्स स्लैब के हिसाब से टैक्सेबल होता है।</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>₹1,00,000 की 1 साल की FD मैच्योर होने पर आपको **₹1,06,398.02** मिलेंगे।
-इसमें से ₹6,398.02 ब्याज है। ध्यान रखें कि इस ब्याज पर आपकी आयकर स्लैब के हिसाब से टैक्स लगेगा।
-SBI का यह रेट 15 दिसंबर 2025 से लागू है।</t>
+          <t>1 लाख रुपये की 1 साल की FD मैच्योर होने पर आपको ₹1,06,398.02 मिलेंगे। इसमें ₹6,398.02 ब्याज शामिल है।
+ये रेट SBI के 15 दिसंबर 2025 से लागू हो रहे हैं। ध्यान रखें कि FD पर जो ब्याज मिलता है, वो आपकी आय टैक्स स्लैब के हिसाब से टैक्सेबल होता है।</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -629,17 +618,12 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>23</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>23.9</v>
+        <v>9</v>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>no loss</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -652,14 +636,16 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SBI के सेविंग्स अकाउंट पर **2.5%** वार्षिक ब्याज मिलता है।
-यह दर 15 जून 2025 से लागू है (स्रोत: SBI)। ध्यान दें कि अब ₹10 लाख से अधिक के बैलेंस पर भी यही दर लगेगी — ऊपर की राशि पर कोई अलग ब्याज नहीं मिलता।</t>
+          <t>State Bank of India (SBI) में सेविंग्स अकाउंट पर **2.5%** वार्षिक ब्याज मिलता है।
+यह दर 15 जून 2025 से लागू है। SBI अब बैलेंस की राशि के आधार पर अलग-अलग ब्याज नहीं देता — चाहे खाते में ₹1 हो या ₹1 करोड़, सभी को यह एक ही दर (2.5%) मिलती है।
+ध्यान दें: छोटी वित्त कंपनियाँ (small finance banks) इससे अधिक ब्याज दे सकती हैं, इसलिए SBI की यह दर बाजार में सबसे कम दरों में से एक है।</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>SBI के सेविंग अकाउंट पर **2.50%** प्रतिवर्ष का ब्याज मिलता है।
-यह दर 15 जून 2025 से लागू है। ध्यान रहे कि अब SBI में खाते के बैलेंस की मात्रा (चाहे ₹10 लाख हो या उससे अधिक) के आधार पर अलग-अलग ब्याज नहीं दिया जाता; एक ही दर सभी खाताधारकों के लिए लागू होती है।</t>
+          <t>State Bank of India (SBI) में सेविंग अकाउंट पर **2.5%** प्रतिवर्ष का ब्याज मिलता है।
+यह दर **15 जून 2025** से लागू है। SBI के नियम के अनुसार, खाते में कितनी भी राशि (₹10 लाख या उससे अधिक) क्यों न हो, यह एक ही दर (2.5%) सभी बैलेंस पर लागू होती है।
+ध्यान दें: यह दर SBI की अपनी कार्ड पर दी गई है। छोटी वित्त बैंक (small finance banks) में कभी-कभी इससे अधिक ब्याज मिल सकता है, इसलिए इसे आप एक आधार मान सकते हैं।</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -677,23 +663,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>NO — lost 1, 1e+07</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12.7</v>
+        <v>5.3</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13.7</v>
+        <v>6.3</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>no loss</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -706,18 +687,16 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>सबसे सस्ता बीमा **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY)** है।
-इसमें सालाना प्रीमियम केवल **₹20** लगता है, जो हर महीने ₹1.67 बनता है। आपकी मासिक कमाई ₹15,000 है, तो यह राशि आपके लिए बिल्कुल सहज है।
-ध्यान रखें: PMSBY में केवल **अपघातजनित मृत्यु या अक्षमता** (accidental death/disability) का ही कवर होता है। बीमारी या प्राकृतिक कारणों से मृत्यु इसमें शामिल नहीं है।
-यदि आप बीमारी सहित किसी भी कारण से होने वाली मृत्यु के लिए सुरक्षा चाहते हैं, तो **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY)** लें। इसका प्रीमियम ₹436 सालाना है, लेकिन यह 'any cause' (किसी भी कारण) की मृत्यु को कवर करता है।
-दोनों ही सरकार द्वारा समर्थित हैं और आपके बैंक खाते से ऑटो-डेबिट होते हैं।</t>
+          <t>सबसे सस्ता बीमा विकल्प **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY)** है, जिसका वार्षिक प्रीमियम केवल **₹20** है।
+ध्यान रखें: PMSBY में कवरेज सिर्फ़ **अकस्मात मृत्यु या अक्षमता** (accidental death/disability) तक सीमित है — बीमारी से होने वाली मृत्यु इसमें शामिल नहीं है।
+यदि आप किसी भी कारण से मृत्यु का कवरेज चाहते हैं, तो **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY)** लें, जिसका प्रीमियम **₹436** प्रति वर्ष है।</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>सबसे सस्ता बीमा **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY)** है। इसमें सालाना प्रीमियम केवल **₹20** लगता है।
-ध्यान रखें: PMSBY में कवरेज सिर्फ़ **अकस्मात मृत्यु या अक्षमता (accidental death/disability)** के लिए होता है, बीमारी से होने वाली मृत्यु के लिए नहीं।
-अगर आपको बीमारी सहित किसी भी कारण से मृत्यु का कवरेज चाहिए, तो **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY)** लें। इसका प्रीमियम ₹436 सालाना है।</t>
+          <t>सबसे सस्ता बीमा विकल्प **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY)** है, जिसका वार्षिक प्रीमियम केवल **₹20** है।
+ध्यान रखें: PMSBY में कवरेज सिर्फ़ **अकस्मात मृत्यु या अक्षमता** (accidental death/disability) तक सीमित है — बीमारी से होने वाली मृत्यु इसमें शामिल नहीं है।
+यदि आप किसी भी कारण से मृत्यु का कवरेज चाहते हैं, तो **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY)** लें, जिसका प्रीमियम **₹436** प्रति वर्ष है।</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -735,23 +714,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>NO — lost 1.67, 15000</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>17.8</v>
+        <v>8.6</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17.9</v>
+        <v>9.4</v>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>NO — trimmed the Rs1.67/month working and the echo of the user's own income. Rs20, Rs436, accident-only vs any-cause all retained.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -764,14 +738,16 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PPF का पूरा नाम Public Provident Fund है। यह सरकार द्वारा संचालित एक सुरक्षित लॉन्ग-टर्म बचत विकल्प है, जिसमें आप हर साल न्यूनतम ₹500 और अधिकतम ₹1.5 लाख जमा कर सकते हैं।
-इस पर मिलने वाला ब्याज 7.1 प्रतिशत है, जो प्रत्येक तिमाही में सरकार द्वारा समीक्षा किया जाता है। यह दर 1 जुलाई 2026 से लागू है।</t>
+          <t>PPF का पूरा नाम Public Provident Fund है। यह सरकार द्वारा संचालित एक लंबी अवधि की बचत योजना है जिसमें आप हर साल निवेश कर सकते हैं।
+इसमें आपको **7.10%** प्रतिवर्ष का ब्याज मिलता है।
+ध्यान दें: यह दर 1 जुलाई 2026 से लागू हुई थी और सरकार हर तिमाही में इन दरों की समीक्षा करती है, इसलिए भविष्य में यह बदल सकती है।</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PPF का पूरा नाम Public Provident Fund है। यह सरकार द्वारा संचालित एक सुरक्षित लॉन्ग-टर्म बचत विकल्प है, जिसमें आप हर साल न्यूनतम ₹500 और अधिकतम ₹1.5 लाख जमा कर सकते हैं।
-इस पर मिलने वाला ब्याज 7.1 प्रतिशत है, जो प्रत्येक तिमाही में सरकार द्वारा समीक्षा किया जाता है। यह दर 1 जुलाई 2026 से लागू है।</t>
+          <t>PPF का पूरा नाम Public Provident Fund है। यह सरकार द्वारा संचालित एक लंबी अवधि की बचत योजना है जिसमें आप हर साल निवेश कर सकते हैं।
+इसमें आपको **7.10%** प्रतिवर्ष का ब्याज मिलता है।
+ध्यान दें: यह दर 1 जुलाई 2026 से लागू हुई थी और सरकार हर तिमाही में इन दरों की समीक्षा करती है, इसलिए भविष्य में यह बदल सकती है।</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -795,17 +771,12 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>11.8</v>
+        <v>7.1</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>12.6</v>
+        <v>7.7</v>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>no loss</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -818,34 +789,50 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62 साल की उम्र में आप सीनियर सिटीजन के तहत बेहतर ब्याज दरें पा सकते हैं। यहाँ कुछ विकल्प दिए गए हैं:
-1. **बैंक FD (सेनियर सिटीजन)**: SBI जैसे बैंकों में 12 महीने की FD पर सीनियर सिटीजन के लिए लगभग 6.75% प्रति वर्ष मिल सकता है। यह दर हर तिमाही में बदल सकती है, इसलिए अपने बैंक से पुष्टि करें।
-2. **सीनियर सिटीजन सेविंग्स स्कीम (SCSS)**: यह सरकार की एक योजना है जिसमें वर्तमान में लगभग 8.2% प्रति वर्ष का ब्याज मिलता है। इसमें आपको हर तिमाही में ब्याज मिलता है, जो नियमित आय के लिए अच्छा विकल्प हो सकता है।
-3. **पोस्ट ऑफिस मंथली इनकम स्कीम (POMIS)**: यदि आप हर महीने कुछ निश्चित राशि चाहते हैं, तो यह योजना उपयुक्त है। इसमें वर्तमान में लगभग 7.4% प्रति वर्ष का ब्याज मिलता है, जो मासिक आधार पर दिया जाता है।
-4. **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY)**: यदि आपका उद्देश्य केवल सुरक्षा है और साथ ही थोड़ी बचत भी करनी है, तो यह योजना ₹436 प्रति वर्ष की प्रीमियम राशि पर 2 लाख रुपये का जीवन बीमा कवरेज देती है।
-5. **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY)**: यह योजना केवल दुर्घटनाजनित मृत्यु और विकलांगता के लिए ₹20 प्रति वर्ष की प्रीमियम राशि पर 2 लाख रुपये का कवरेज देती है।
-6. **अटल पेंशन योजना (APY)**: यदि आप 60 साल की उम्र के बाद मासिक पेंशन चाहते हैं, तो यह योजना उपयुक्त है। इसमें आपको 1,000 से 5,000 रुपये प्रति माह की पेंशन मिल सकती है।
-7. **किसान विकास पत्र (KVP)**: यह एक अन्य सरकारी बचत योजना है जिसमें वर्तमान में लगभग 7.5% प्रति वर्ष का ब्याज मिलता है।
-8. **प्रगतिशील सेविंग्स स्कीम (PPF)**: यह एक लंबी अवधि की बचत योजना है जिसमें वर्तमान में लगभग 7.1% प्रति वर्ष का ब्याज मिलता है।
-9. **सुकन्या समृद्धि योजना (SSY)**: यदि आपकी बेटी है, तो यह योजना उनके भविष्य के लिए अच्छा विकल्प हो सकता है। इसमें वर्तमान में लगभग 8.2% प्रति वर्ष का ब्याज मिलता है।
-10. **राष्ट्रीय बचत प्रमाणपत्र (NSC)**: यह एक अन्य सरकारी बचत योजना है जिसमें वर्तमान में लगभग 7.7% प्रति वर्ष का ब्याज मिलता है।
-इन सभी विकल्पों के बारे में अधिक जानकारी के लिए, आप अपने नजदीकी बैंक या डाकघर से संपर्क कर सकते हैं।</t>
+          <t>आपकी उम्र (62 वर्ष) के आधार पर आप 'सीनियर सिटीजन' श्रेणी में आते हैं। सरकार द्वारा चलाए जाने वाले छोटे बचत योजनाओं (Small Savings Schemes) का ब्याज दर आम FD से अधिक है, इसलिए वे आपके लिए बेहतर विकल्प हो सकते हैं।
+यहाँ 62 वर्षीय व्यक्ति के लिए उपलब्ध प्रमुख विकल्प और उनके वर्तमान ब्याज दर दिए गए हैं:
+1. **सीनियर सिटीजन सेविंग्स स्कीम (SCSS)**
+   - **ब्याज दर:** 8.2% प्रति वर्ष
+   - **स्रोत:** वित्त मंत्रालय (आर्थिक कार्य विभाग)
+   - **प्रभावी तिथि:** 1 जुलाई 2026 से
+   - **विशेषता:** यह योजना विशेष रूप से सीनियर सिटीजन के लिए है। ब्याज दरें हर तिमाही में संशोधित की जा सकती हैं, इसलिए अगली तिमाही (1 अक्टूबर 2026) में रेट बदल सकता है।
+2. **राष्ट्रीय बचत प्रमाणपत्र (NSC)**
+   - **ब्याज दर:** 7.7% प्रति वर्ष
+   - **स्रोत:** वित्त मंत्रालय (आर्थिक कार्य विभाग)
+   - **प्रभावी तिथि:** 1 जुलाई 2026 से
+   - **विशेषता:** यह एक लॉन्ग-टर्म निवेश है। SCSS की तुलना में इसकी बचत दर थोड़ी कम है, लेकिन यह भी सुरक्षित विकल्प है।
+3. **बैंक FD (सिनियर सिटीजन रेट)**
+   - **उदाहरण के लिए SBI:** 1 वर्ष की अवधि के लिए 6.75% प्रति वर्ष
+   - **स्रोत:** State Bank of India
+   - **प्रभावी तिथि:** 15 दिसंबर 2025 से
+   - **विशेषता:** SBI में 60 वर्ष और उससे अधिक उम्र के ग्राहकों को बेस रेट पर 0.5% का बोनस मिलता है।
+**निष्कर्ष:**
+अगर आपका मुख्य उद्देश्य नियमित और उच्च इनकम है, तो **SCSS (8.2%)** वर्तमान में सबसे अच्छा विकल्प प्रतीत होता है क्योंकि इसकी ब्याज दर NSC (7.7%) और SBI FD (6.75%) दोनों से अधिक है।
+ध्यान दें: छोटी बचत योजनाओं की दरें हर तिमाही में बदल सकती हैं, इसलिए निवेश करने से पहले नवीनतम रेट की पुष्टि अवश्य करें।</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62 साल की उम्र में आप सीनियर सिटीजन के तहत बेहतर ब्याज दरें पा सकते हैं। यहाँ कुछ विकल्प दिए गए हैं:
-1. **बैंक FD (सेनियर सिटीजन)**: SBI जैसे बैंकों में 12 महीने की FD पर सीनियर सिटीजन के लिए लगभग 6.75% प्रति वर्ष मिल सकता है। यह दर हर तिमाही में बदल सकती है, इसलिए अपने बैंक से पुष्टि करें।
-2. **सीनियर सिटीजन सेविंग्स स्कीम (SCSS)**: यह सरकार की एक योजना है जिसमें वर्तमान में लगभग 8.2% प्रति वर्ष का ब्याज मिलता है। इसमें आपको हर तिमाही में ब्याज मिलता है, जो नियमित आय के लिए अच्छा विकल्प हो सकता है।
-3. **पोस्ट ऑफिस मंथली इनकम स्कीम (POMIS)**: यदि आप हर महीने कुछ निश्चित राशि चाहते हैं, तो यह योजना उपयुक्त है। इसमें वर्तमान में लगभग 7.4% प्रति वर्ष का ब्याज मिलता है, जो मासिक आधार पर दिया जाता है।
-4. **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY)**: यदि आपका उद्देश्य केवल सुरक्षा है और साथ ही थोड़ी बचत भी करनी है, तो यह योजना ₹436 प्रति वर्ष की प्रीमियम राशि पर 2 लाख रुपये का जीवन बीमा कवरेज देती है।
-5. **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY)**: यह योजना केवल दुर्घटनाजनित मृत्यु और विकलांगता के लिए ₹20 प्रति वर्ष की प्रीमियम राशि पर 2 लाख रुपये का कवरेज देती है।
-6. **अटल पेंशन योजना (APY)**: यदि आप 60 साल की उम्र के बाद मासिक पेंशन चाहते हैं, तो यह योजना उपयुक्त है। इसमें आपको 1,000 से 5,000 रुपये प्रति माह की पेंशन मिल सकती है।
-7. **किसान विकास पत्र (KVP)**: यह एक अन्य सरकारी बचत योजना है जिसमें वर्तमान में लगभग 7.5% प्रति वर्ष का ब्याज मिलता है।
-8. **प्रगतिशील सेविंग्स स्कीम (PPF)**: यह एक लंबी अवधि की बचत योजना है जिसमें वर्तमान में लगभग 7.1% प्रति वर्ष का ब्याज मिलता है।
-9. **सुकन्या समृद्धि योजना (SSY)**: यदि आपकी बेटी है, तो यह योजना उनके भविष्य के लिए अच्छा विकल्प हो सकता है। इसमें वर्तमान में लगभग 8.2% प्रति वर्ष का ब्याज मिलता है।
-10. **राष्ट्रीय बचत प्रमाणपत्र (NSC)**: यह एक अन्य सरकारी बचत योजना है जिसमें वर्तमान में लगभग 7.7% प्रति वर्ष का ब्याज मिलता है।
-इन सभी विकल्पों के बारे में अधिक जानकारी के लिए, आप अपने नजदीकी बैंक या डाकघर से संपर्क कर सकते हैं।</t>
+          <t>आपकी उम्र (62 वर्ष) के आधार पर आप 'सीनियर सिटीजन' श्रेणी में आते हैं। सरकार द्वारा चलाए जाने वाले छोटे बचत योजनाओं (Small Savings Schemes) का ब्याज दर आम FD से अधिक है, इसलिए वे आपके लिए बेहतर विकल्प हो सकते हैं।
+यहाँ 62 वर्षीय व्यक्ति के लिए उपलब्ध प्रमुख विकल्प और उनके वर्तमान ब्याज दर दिए गए हैं:
+1. **सीनियर सिटीजन सेविंग्स स्कीम (SCSS)**
+   - **ब्याज दर:** 8.2% प्रति वर्ष
+   - **स्रोत:** वित्त मंत्रालय (आर्थिक कार्य विभाग)
+   - **प्रभावी तिथि:** 1 जुलाई 2026 से
+   - **विशेषता:** यह योजना विशेष रूप से सीनियर सिटीजन के लिए है। ब्याज दरें हर तिमाही में संशोधित की जा सकती हैं, इसलिए अगली तिमाही (1 अक्टूबर 2026) में रेट बदल सकता है।
+2. **राष्ट्रीय बचत प्रमाणपत्र (NSC)**
+   - **ब्याज दर:** 7.7% प्रति वर्ष
+   - **स्रोत:** वित्त मंत्रालय (आर्थिक कार्य विभाग)
+   - **प्रभावी तिथि:** 1 जुलाई 2026 से
+   - **विशेषता:** यह एक लॉन्ग-टर्म निवेश है। SCSS की तुलना में इसकी बचत दर थोड़ी कम है, लेकिन यह भी सुरक्षित विकल्प है।
+3. **बैंक FD (सिनियर सिटीजन रेट)**
+   - **उदाहरण के लिए SBI:** 1 वर्ष की अवधि के लिए 6.75% प्रति वर्ष
+   - **स्रोत:** State Bank of India
+   - **प्रभावी तिथि:** 15 दिसंबर 2025 से
+   - **विशेषता:** SBI में 60 वर्ष और उससे अधिक उम्र के ग्राहकों को बेस रेट पर 0.5% का बोनस मिलता है।
+**निष्कर्ष:**
+अगर आपका मुख्य उद्देश्य नियमित और उच्च इनकम है, तो **SCSS (8.2%)** वर्तमान में सबसे अच्छा विकल्प प्रतीत होता है क्योंकि इसकी ब्याज दर NSC (7.7%) और SBI FD (6.75%) दोनों से अधिक है।
+ध्यान दें: छोटी बचत योजनाओं की दरें हर तिमाही में बदल सकती हैं, इसलिए निवेश करने से पहले नवीनतम रेट की पुष्टि अवश्य करें।</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -869,17 +856,12 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>32.8</v>
+        <v>15.9</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>33.7</v>
+        <v>16.8</v>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>no loss</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -892,26 +874,21 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SBI में बचत खाता खोलने के लिए आपको दो तरह के दस्तावेज चाहिए:
-1. **पते और नाम का सबूत (Proof of Name &amp; Address):** इनमें से कोई एक:
-   - आधार कार्ड (Aadhaar)
-   - वोटर आईडी (Voter ID)
-   - NREGA जॉब कार्ड
-   - नेशनल पॉपुलेशन रजिस्टर (NPR) का पत्र
-2. **आयकर पहचान (PAN):**
-   - अपना PAN कार्ड, या
-   - अगर आपके पास PAN नहीं है, तो **फॉर्म 60** भरें।
-अगर आप केवल आधार कार्ड दे रहे हैं, तो वह पते और नाम दोनों का सबूत माना जाएगा।
-सभी जानकारी RBI के KYC दिशानिर्देशों के अनुसार है।</t>
+          <t>SBI में बचत खाता खोलने के लिए आपको तीन चीज़ें जमा करनी होंगी:
+1. **पते और नाम का सबूत (OVD):** इनमें से कोई एक — आधार कार्ड, वोटर आईडी, NREGA जॉब कार्ड, या नेशनल पॉपुलेशन रजिस्टर का लेटर।
+2. **आयकर पहचान:** PAN कार्ड। अगर आपके पास PAN नहीं है, तो फॉर्म 60 भरना होगा।
+3. **व्यक्तिगत जानकारी:** आपका फोटो और हस्ताक्षर।
+**ध्यान दें:** अगर आपके पास ऊपर दी गई कोई भी KYC दस्तावेज़ नहीं है, तो SBI आपको एक 'Small Account' खोलकर दे सकता है। इसमें शुरुआत में राशि सीमित (₹50,000 से अधिक बैलेंस नहीं) होती है, लेकिन आप बाद में पूरा KYC करके इसे सामान्य खाते में बदल सकते हैं।</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SBI में बचत खाता खोलने के लिए आपको दो तरह के दस्तावेज चाहिए, जो RBI की KYC गाइडलाइन के तहत हैं:
-1. **पहचान और पते का सबूत (OVD):** इनमें से कोई एक जरूरी है — आधार कार्ड, वोटर आईडी, NREGA जॉब कार्ड, या नेशनल पॉपुलेशन रजिस्टर की लेटर।
-2. **आयकर पहचान:** PAN कार्ड। अगर आपके पास PAN नहीं है, तो आपको फॉर्म 60 भरना होगा।
-**ध्यान दें:** ये नियम SBI के अपने हैं (RBI का स्रोत: *Master Direction on KYC*, SBI का स्रोत: *Savings Bank Rules*)।
-अगर आपके पास ऊपर दिए गए दस्तावेज नहीं हैं, तो आप **Small Account** खोल सकते हैं। इसमें बस एक फोटो और हस्ताक्षर (या अंगूठे का निशान) चाहिए होता है, लेकिन इस खाते में पैसे जमा करने की सीमा ₹50,000 तक होती है।</t>
+          <t>SBI में बचत खाता खोलने के लिए आपको तीन चीज़ें जमा करनी होंगी:
+1. **पहचान और पता साबित करने वाला दस्तावेज़ (OVD):** इनमें से कोई एक — आधार कार्ड, वोटर आईडी, या NREGA जॉब कार्ड।
+2. **आयकर पहचान (PAN):** अपना PAN कार्ड या Form 60 (अगर आपके पास PAN नहीं है)।
+3. **व्यापार/वित्तीय स्थिति:** अगर खाता किसी व्यापार के लिए है, तो उससे जुड़े दस्तावेज़।
+**ध्यान दें:** अगर आपके पास ऊपर दिए गए कोई भी KYC दस्तावेज़ नहीं हैं, तो आप SBI में एक 'Small Account' खोल सकते हैं। इसमें आपको 50,000 रुपये से ज़्यादा बैलेंस नहीं रखना है और महीने में सिर्फ 10,000 रुपये ही निकालने हैं। जब तक आप पूरा KYC नहीं करते, यह खाता तभी तक चलता है।
+अगर आप एक 'Basic Savings Bank Deposit Account' (BSBD) खोलते हैं, तो उसमें कोई न्यूनतम बैलेंस रखने की ज़रूरत नहीं है, लेकिन इस शर्त पर कि आपके पास SBI में कोई दूसरा आम बचत खाता नहीं होना चाहिए।</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -935,17 +912,12 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>20.6</v>
+        <v>10.1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21.8</v>
+        <v>11.2</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>no loss</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -959,15 +931,17 @@
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>अगर बैंक डूब जाता है, तो आपका पैसा **₹5,00,000** तक सुरक्षित है।
-यह कवर प्रिंसिपल (मूल राशि) और ब्याज दोनों को मिलाकर ₹5 लाख तक का है। यह RBI की डिपॉजिट इन्श्योरेंस गारंटी कॉर्पोरेशन (DICGC) के तहत मिलता है।
-ध्यान रखें: अगर आपके पास उसी बैंक में एक से ज्यादा अकाउंट्स हैं, तो सभी राशियों को जोड़कर ₹5 लाख का कवर लागू होता है।</t>
+यह कवरेज RBI के तहत DICGC (Deposit Insurance and Credit Guarantee Corporation) द्वारा दिया गया है। इसमें आपके मूल धन राशि और उस पर लगा ब्याज दोनों शामिल हैं।
+ध्यान रखें: एक ही बैंक में आपकी सभी जमा राशियाँ (सभी शाखाओं की) जोड़कर ₹5 लाख का कवरेज लागू होता है। अगर आपके पास ₹5 लाख से ज्यादा पैसे हैं, तो बाकी राशि सुरक्षित नहीं मानी जाएगी।
+स्रोत: RBI FAQ — Deposit Insurance (DICGC)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>अगर बैंक डूब जाता है, तो आपका पैसा **₹5,00,000** तक सुरक्षित है।
-यह कवर प्रिंसिपल (मूल राशि) और ब्याज दोनों को मिलाकर ₹5 लाख तक का है। यह RBI की डिपॉजिट इन्श्योरेंस गारंटी कॉर्पोरेशन (DICGC) के तहत मिलता है।
-ध्यान रखें: अगर आपके पास उसी बैंक में एक से ज्यादा अकाउंट्स हैं, तो सभी राशियों को जोड़कर ₹5 लाख का कवर लागू होता है।</t>
+यह कवरेज RBI के तहत DICGC (Deposit Insurance and Credit Guarantee Corporation) द्वारा दिया गया है। इसमें आपके मूल धन राशि और उस पर लगा ब्याज दोनों शामिल हैं।
+ध्यान रखें: एक ही बैंक में आपकी सभी जमा राशियाँ (सभी शाखाओं की) जोड़कर ₹5 लाख का कवरेज लागू होता है। अगर आपके पास ₹5 लाख से ज्यादा पैसे हैं, तो बाकी राशि सुरक्षित नहीं मानी जाएगी।
+स्रोत: RBI FAQ — Deposit Insurance (DICGC)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -991,17 +965,12 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15</v>
+        <v>8.9</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>15.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>no loss</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1014,30 +983,35 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>जीरो बैलेंस खाता वह है जिसमें न्यूनतम शेष राशि (minimum balance) रखने की जरूरत नहीं होती। अगर बैलेंस शून्य भी रहता है तो कोई चार्ज नहीं लगता।
-**कौन खोल सकता है?**
-RBI के नियमों के तहत, **कोई भी व्यक्ति** जो मान्य KYC दस्तावेज़ (जैसे आधार, वोटर आईडी, पासपोर्ट) रखता है, जीरो बैलेंस खाता खोल सकता है। यह गरीब वर्ग को बैंकिंग में लाने के लिए बनाया गया है।
-**मुख्य बातें:**
-1. **प्रधानमंत्री जन धन योजना (PMJDY):** यह सरकार की मुख्य स्कीम है। इसमें खाता खोलने पर आपको एक **रुपे डेबिट कार्ड** मिलता है और **₹2,00,000** का एक्सीडेंट इंश्योरेंस कवर (उन खातों के लिए जो 28 अगस्त 2018 के बाद खुले) उपलब्ध होता है।
-2. **बेसिक सेविंग्स बैंक डिपॉजिट (BSBD) खाता:** सभी बड़ी बैंकें (जैसे SBI, PNB आदि) अपने आप BSBD खाते भी देती हैं जो जीरो बैलेंस पर चलते हैं।
-**ध्यान रखें:**
-अगर आप किसी बैंक में 'बेसिक' या 'जीरो बैलेंस' खाता खोलते हैं, तो उसी बैंक में आपके पास कोई अन्य सामान्य सेविंग्स खाता नहीं होना चाहिए। अगर पहले से खाता है, तो उसे बंद करना होगा।
-**आवश्यक दस्तावेज़:**
-- पहचान पत्र (Aadhaar, वोटर आईडी, पासपोर्ट आदि)
-- पता प्रमाण (Aadhaar, बिजली का बिल, आदि)
-अगर आपका मतलब 'खुलासा खाता' (unbanked) है जिसमें KYC की सख्त जरूरत नहीं होती, तो RBI के 'Small Account' नियम के तहत कुछ शर्तों के साथ ऐसा खाता भी दिया जा सकता है, लेकिन उसमें राशि जमा करने की सीमा होती है।</t>
+          <t>जीरो बैलेंस खाता वह है जिसमें आपको न्यूनतम बैलेंस रखने की जरूरत नहीं होती। भारत में इसका मतलब आमतौर पर दो अलग-अलग खातों से है, और कौन खोल सकता है, यह इस बात पर निर्भर करता है कि आपके पास KYC (पहचान) के कागजात हैं या नहीं:
+1. **Basic Savings Bank Deposit Account (BSBD)**
+   - **कौन खोल सकता है:** कोई भी व्यक्ति, बशर्ते उसके पास मान्य KYC दस्तावेज हों।
+   - **विशेषता:** यह पूरी तरह से KYC-अनुपालन खाता है।
+   - **महत्वपूर्ण शर्त (SBI नियम के अनुसार):** आप BSBD खोल सकते हैं, लेकिन यदि आपके पास पहले से कोई अन्य Savings Bank Account है, तो आपको उसे 30 दिनों के भीतर बंद करना होगा। एक समय में केवल एक ही BSBD खाता रखा जा सकता है।
+2. **Small Account (Limited KYC)**
+   - **कौन खोल सकता है:** 18 वर्ष से ऊपर का कोई भी व्यक्ति जो Officially Valid KYC दस्तावेज प्रस्तुत नहीं कर पा रहा है।
+   - **शर्तें:** इसमें बैलेंस ₹50,000 तक हो सकता है और माह में कुल निकासी/ट्रांसफर ₹10,000 तक सीमित है। यदि आप बाद में KYC दस्तावेज जमा कराते हैं, तो इसे नियमित Savings Account में बदला जा सकता है।
+**आवश्यक दस्तावेज (KYC के लिए):**
+RBI के निर्देशों के अनुसार, खाता खोलने के लिए आपको निम्नलिखित में से एक Officially Valid Document (OVD) की जरूरत होगी:
+- Aadhaar नंबर का प्रमाण
+- वोटर आईडी कार्ड
+- NREGA जॉब कार्ड
+- राष्ट्रीय जनगणना रजिस्टर द्वारा जारी पत्र
+इसके अलावा, आपका नाम और पता साबित करने के लिए PAN कार्ड (या यदि PAN नहीं है तो Form 60) की आवश्यकता होगी।</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>जीरो बैलेंस खाता वह है जिसमें आपको न्यूनतम बैलेंस रखने की जरूरत नहीं होती और इस पर कोई चार्ज नहीं लगता।
-**कौन खोल सकता है:**
-1. **PMJDY (प्रधानमंत्री जन धन योजना):** यह सरकार का स्कीम है। किसी भी व्यक्ति को, जो पहले से बैंक में खाता नहीं रखता, इसे खोलने की अनुमति है। इसमें ₹2 लाख तक का एक्सीडेंट इंश्योरेंस और ₹10,000 का ओवरड्राफ्ट फेसिलिटी मिलती है (source: PMJDY scheme details).
-2. **BSBD खाता:** यह बैंकों द्वारा दिया जाने वाला जीरो बैलेंस खाता है। इसे खोलने के लिए वैध KYC दस्तावेजों की जरूरत होती है। ध्यान रहे, अगर आपके पास पहले से कोई अन्य सेविंग्स अकाउंट है, तो आपको उसे बंद करना होगा (source: SBI BSBD terms).
-**सुविधाएं:**
-- न्यूनतम बैलेंस की जरूरत नहीं।
-- मुफ्त रूपाय डेबिट कार्ड।
-- NEFT/RTGS से पैसे आने पर कोई चार्ज नहीं।</t>
+          <t>जीरो बैलेंस खाता वह है जिसमें आपको न्यूनतम बैलेंस रखने की जरूरत नहीं होती और इस पर कोई मेंटेनेंस चार्ज नहीं लगता। यह मुख्य रूप से दो तरह के होते हैं:
+1. **बेसिक सेविंग्स बैंक डिपॉजिट (BSBD) खाता**: यह RBI के नियमों के तहत हर किसी को खुलवाया जा सकता है। इसमें न्यूनतम बैलेंस शून्य होता है, लेकिन आप एक ही समय में केवल एक BSBD खाता रख सकते हैं और यदि आपके पास पहले से कोई सामान्य सेविंग्स अकाउंट है तो उसे बंद करना होगा।
+2. **प्रधानमंत्री जन धन योजना (PMJDY)**: यह सरकार की एक पहल है जो हर नागरिक को जीरो बैलेंस खाता खोलने और ₹10,000 तक का ओवरड्राफ्ट सुविधा प्रदान करने के लिए प्रोत्साहित करती है।
+**कागजात (KYC) की आवश्यकता:**
+खाता खोलने के लिए KYC अनिवार्य है। आपको निम्नलिखित दस्तावेजों में से एक या अधिक देना होगा:
+- आधार कार्ड
+- वोटर्स आईडी
+- NREGA जॉब कार्ड
+- नेशनल पॉपुलेशन रजिस्टर (NPR) का पत्र
+- PAN कार्ड (या यदि PAN नहीं है तो फॉर्म 60)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1057,21 +1031,16 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>NO — lost 28, 2018</t>
+          <t>NO — lost 18, 30, 50000</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>22.5</v>
+        <v>15.2</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>21.1</v>
+        <v>15.4</v>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>MINOR — lost the "opened after 28 Aug 2018" qualifier. Rs2 lakh cover retained (written in words). Styled version ADDED the Rs10,000 overdraft, source attribution and free NEFT/RTGS — net better.</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1084,22 +1053,20 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,000 रुपये की सैलरी के लिए पैसा बांटने का सबसे आसान तरीका 50-30-20 नियम है। इसमें आपकी मासिक बचत (savings) 6,000 रुपये बनती है।
-यहाँ देखिए कि यह राशि कैसे टूटती है:
-* **जरूरतें (Needs): ₹15,000** — किराया, खाना, बिजली के बिल, और यात्रा जैसे फिक्स खर्च।
-* **चाहें (Wants): ₹9,000** — बाहर का खाना, शॉपिंग, मूवीज या हॉबीज।
-* **बचत/निवेश (Savings): ₹6,000** — यह वह राशि है जो आपको अगले महीने में ही निवेश कर देनी चाहिए।
-**शुरुआत के लिए एक छोटा सा टिप:**
-सबसे पहले इस 6,000 रुपये में से एक Emergency Fund (आपातकालीन फंड) शुरू करें। कम से कम 3-6 महीने के खर्च के बराबर राशि को एक अलग बैंक खाते में जमा रखें ताकि कोई अनपेक्षित खर्च आने पर आप लोन न लेने मजबूर हों।</t>
+          <t>30,000 रुपये की सैलरी के लिए आप पैसों को इस तरह बांट सकते हैं:
+• **आवश्यक खर्च (Needs): ₹15,000** — किराया, भोजन, बिल और यातायात जैसे जरूरी खर्च।
+• **चाहें (Wants): ₹9,000** — मूवीज, शॉपिंग, दोस्तों के साथ घूमना आदि मनोरंजन के लिए।
+• **बचत (Savings): ₹6,000** — यह वह राशि है जो आप भविष्य के लिए जमा करेंगे।
+सबसे पहले एक Emergency Fund (आपातकालीन निधि) बनाएं जिसमें कम से कम 3-6 महीने का खर्च शामिल हो। उसके बाद आप इसे FD, Mutual Funds या अन्य विकल्पों में लगा सकते हैं।</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,000 रुपये की सैलरी पर पैसा कैसे बांटें, इसका एक आसान फॉर्मूला है:
-1. **जरूरतें (Needs): ₹15,000** — इसमें किराया, खाना, बिजली का बिल और यात्रा शामिल है।
-2. **चाहें (Wants): ₹9,000** — यह आपकी पसंद की चीजों के लिए है, जैसे बाहर खाना, शॉपिंग या मूवी।
-3. **बचत (Savings): ₹6,000** — यह वह राशि है जो आपको निवेश में डालनी चाहिए।
-ध्यान रहे: बचत वाली राशि को पहले जमा करें, बाकी खर्चों के लिए न देखें।</t>
+          <t>₹30,000 की सैलरी पर पैसा कैसे बाँटना है, इसका एक सिंपल फॉर्मूला है:
+1. **जरूरतें (Needs): ₹15,000** — रेंट, खाना, बिजली का बिल, यात्रा। ये वो पैसे हैं जो बिना नहीं रह सकते।
+2. **चाहें (Wants): ₹9,000** — मूवी, बाहर खाना, शॉपिंग। इसमें थोड़ी लचीलापन रखें।
+3. **बचत (Savings): ₹6,000** — यह वो पैसे हैं जो आप भविष्य के लिए जमा करेंगे।
+सबसे पहले एक Emergency Fund (आपातकालीन निधि) बनाएं जिसमें कम से कम 3-6 महीने का खर्च आ जाए। उसके बाद आप SIP या FD जैसे विकल्पों पर विचार कर सकते हैं।</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1117,23 +1084,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>NO — lost 6, 20, 30, 50</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>22</v>
+        <v>13.1</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22</v>
+        <v>13.9</v>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>YES — dropped the emergency-fund advice (3-6 months of expenses set aside) and the "50-30-20" rule name. The only material loss in the set.</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1147,14 +1109,14 @@
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>SBI के होम लोन पर ब्याज दरें **₹7.25% से शुरू** होती हैं।
-यह रेट 1 अप्रैल 2026 से लागू है (स्रोत: SBI)। ध्यान रखें कि यह 'शुरुआती' दर है — आपकी वास्तविक दर आपकी क्रेडिट स्कोर और प्रोफाइल पर निर्भर करेगी, जो अक्सर इससे अधिक हो सकती है।</t>
+हालाँकि, ध्यान रखें कि ये दरें केवल शुरुआती (starting) दरें हैं। आपकी वास्तविक ब्याज दर आपकी क्रेडिट स्कोर और प्रोफाइल पर निर्भर करेगी, जो आमतौर पर इनसे अधिक हो सकती है।
+ये दरें **1 अप्रैल 2026** से लागू हैं।</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>State Bank of India के अनुसार होम लोन पर ब्याज दर **7.25% से शुरू** होती है।
-यह दर **1 अप्रैल 2026** से लागू है। ध्यान रहे कि यह 'शुरू होने वाली' (starting) दर है — अंतिम दर आपकी क्रेडिट स्कोर और अन्य प्रोफाइल के आधार पर इससे अधिक हो सकती है।
-स्रोत: SBI की आधिकारिक ब्याज दर कार्ड।</t>
+          <t>State Bank of India की वर्तमान होम लोन ब्याज दरें **7.25% से शुरू होकर 8.45%** तक हैं।
+ये दरें 1 अप्रैल 2026 से लागू हैं। ध्यान रखें कि ये 'शुरू होने वाली' दरें हैं — आपकी व्यक्तिगत दर आपकी क्रेडिट स्कोर और अन्य प्रोफाइल के आधार पर इससे अलग हो सकती है।</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1178,17 +1140,12 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>no loss</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1201,22 +1158,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>बुढ़ापे के लिए पेंशन का इंतज़ाम करने के लिए आप मुख्य रूप से **अटल पेंशन योजना (APY)** पर ध्यान दे सकते हैं। यह एक सरकारी स्कीम है जिसमें आपको 60 साल की उम्र तक निश्चित मासिक पेंशन मिलती है।
-**अटल पेंशन योजना (APY) के मुख्य बिंदु:**
-*   **पेंशन विकल्प:** आप ₹1,000 से लेकर ₹5,000 प्रति माह की पेंशन चुन सकते हैं।
-*   **योगदान (Contribution):** आपको कितना पैसा जमा करना होगा, यह आपके उम्र पर निर्भर करता है। इसलिए एक निश्चित राशि यहाँ पर नहीं बताई जा सकती — इसे अपने बैंक से संपर्क करके जानें।
-इसके अलावा, आप **सीनियर सिटीजन सेविंग्स स्कीम (SCSS)** और **पोस्ट ऑफिस मंथली इनकम स्कीम (POMIS)** जैसे विकल्पों पर भी विचार कर सकते हैं, जो बुढ़ापे में स्थिर आय के लिए अच्छे माने जाते हैं।
-*नोट: ये रेट 1 जुलाई 2026 से लागू हैं और हर तिमाही में बदल सकते हैं।*</t>
+          <t>बुढ़ापे के लिए पेंशन का इंतज़ाम करने के लिए सरकार की सबसे सीधी स्कीम **अटल पेंशन योजना (APY)** है।
+**अटल पेंशन योजना (APY) कैसे काम करती है:**
+- आप 60 साल की उम्र से हर महीने तयशुदा पेंशन पाएंगे।
+- पेंशन के विकल्प: ₹1,000, ₹2,000, ₹3,000, ₹4,000 या ₹5,000 प्रति माह।
+- जो राशि आपको हर महीने जमा करनी होगी, वह आपकी **उम्र** और चुनी गई पेंशन पर निर्भर करती है। किसी एक निश्चित राशि का दावा नहीं किया जा सकता क्योंकि यह उम्र के साथ बदलता है।
+**अतिरिक्त सुरक्षा (बीमा):**
+पेंशन के साथ-साथ आपकी आर्थिक सुरक्षा के लिए ये दो योजनाएं भी देख सकते हैं:
+1. **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY):** सालाना ₹436 का प्रीमियम देकर ₹2,00,000 का जीवन बीमा मिलता है (किसी भी कारण मृत्यु पर)।
+2. **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY):** सालाना ₹20 का प्रीमियम देकर ₹2,00,000 का बीमा मिलता है (केवल दुर्घटनाजनित मृत्यु और अक्षमता पर, बीमारी से नहीं)।
+इन योजनाओं के लिए आप अपने बैंक या डाक घर में जाकर अपना खाता जोड़ सकते हैं।</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>बुढ़ापे के लिए पेंशन का इंतज़ाम करने के लिए आप मुख्य रूप से **अटल पेंशन योजना (APY)** पर ध्यान दे सकते हैं। यह एक सरकारी स्कीम है जिसमें आपको 60 साल की उम्र तक निश्चित मासिक पेंशन मिलती है।
-**अटल पेंशन योजना (APY) के मुख्य बिंदु:**
-*   **पेंशन विकल्प:** आप ₹1,000 से लेकर ₹5,000 प्रति माह की पेंशन चुन सकते हैं।
-*   **योगदान (Contribution):** आपको कितना पैसा जमा करना होगा, यह आपके उम्र पर निर्भर करता है। इसलिए एक निश्चित राशि यहाँ पर नहीं बताई जा सकती — इसे अपने बैंक से संपर्क करके जानें।
-इसके अलावा, आप **सीनियर सिटीजन सेविंग्स स्कीम (SCSS)** और **पोस्ट ऑफिस मंथली इनकम स्कीम (POMIS)** जैसे विकल्पों पर भी विचार कर सकते हैं, जो बुढ़ापे में स्थिर आय के लिए अच्छे माने जाते हैं।
-*नोट: ये रेट 1 जुलाई 2026 से लागू हैं और हर तिमाही में बदल सकते हैं।*</t>
+          <t>बुढ़ापे के लिए पेंशन का इंतज़ाम करने के लिए सरकार की सबसे सीधी स्कीम **अटल पेंशन योजना (APY)** है।
+**अटल पेंशन योजना (APY) कैसे काम करती है:**
+- आप 60 साल की उम्र से हर महीने तयशुदा पेंशन पाएंगे।
+- पेंशन के विकल्प: ₹1,000, ₹2,000, ₹3,000, ₹4,000 या ₹5,000 प्रति माह।
+- जो राशि आपको हर महीने जमा करनी होगी, वह आपकी **उम्र** और चुनी गई पेंशन पर निर्भर करती है। किसी एक निश्चित राशि का दावा नहीं किया जा सकता क्योंकि यह उम्र के साथ बदलता है।
+**अतिरिक्त सुरक्षा (बीमा):**
+पेंशन के साथ-साथ आपकी आर्थिक सुरक्षा के लिए ये दो योजनाएं भी देख सकते हैं:
+1. **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY):** सालाना ₹436 का प्रीमियम देकर ₹2,00,000 का जीवन बीमा मिलता है (किसी भी कारण मृत्यु पर)।
+2. **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY):** सालाना ₹20 का प्रीमियम देकर ₹2,00,000 का बीमा मिलता है (केवल दुर्घटनाजनित मृत्यु और अक्षमता पर, बीमारी से नहीं)।
+इन योजनाओं के लिए आप अपने बैंक या डाक घर में जाकर अपना खाता जोड़ सकते हैं।</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1240,17 +1205,12 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>29.1</v>
+        <v>10</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>30</v>
+        <v>10.8</v>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>no loss</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1263,7 +1223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1290,6 +1250,9 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+    </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -1311,6 +1274,9 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -1346,41 +1312,13 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>Red cells mean look here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>On the red cells</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>The automated check counts figures; it cannot tell a trimmed aside from a dropped fact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>The last column is a human read of each one. Of 3 flagged rows, 1 is a material loss.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>No answer ever became wrong — nothing was miscounted or invented, only omitted.</t>
         </is>
       </c>
     </row>

--- a/docs/style-comparison-final.xlsx
+++ b/docs/style-comparison-final.xlsx
@@ -530,22 +530,22 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>5 साल की बेटी के लिए **सुकन्या समृद्धि योजना (Sukanya Samriddhi Yojana)** सबसे उपयुक्त सरकारी विकल्प है।
-इसका ब्याज दर वर्तमान में **8.2%** है, जो 1 जुलाई 2026 से लागू है। यह दर हर तिमाही में सरकार द्वारा समीक्षा की जाती है, इसलिए भविष्य में बदलाव हो सकता है।
-इस योजना के मुख्य लाभ:
-* बेटी के लिए लंबे समय तक सुरक्षित निवेश।
-* परिपक्वता पर प्राप्त राशि पर आयकर छूट (Section 80C और 80TTB के तहत)।
-कृपया ध्यान दें: यह जानकारी सामान्य शिक्षा के उद्देश्यों से है। किसी भी योजना में निवेश करने से पहले अपने वित्तीय सलाहकार या CA से अपनी स्थिति के अनुसार पुष्टि अवश्य करें।</t>
+          <t>आपकी बेटी के लिए **सुकन्या समृद्धि योजना (Sukanya Samriddhi Yojana)** सबसे अच्छा विकल्प है।
+यह योजना विशेष रूप से बालिकाओं की शिक्षा और शादी के भविष्य के लिए बनाई गई है:
+* **ब्याज दर:** 8.2% प्रति वर्ष (प्रभावी 1 जुलाई 2026 से)।
+* **लाभ:** यह एक सरकारी योजना है जिसका ब्याज दर सामान्य FD से अधिक होता है और इसमें आयकर की छूट (Section 80C) का लाभ मिलता है।
+**अन्य विकल्प:** आप PPF (Public Provident Fund) भी खोल सकते हैं, जिसकी वर्तमान ब्याज दर 7.1% है। लेकिन बालिकाओं के लिए SSY की दर बेहतर है।
+**ध्यान दें:** छोटी बचत योजनाओं की दरें हर तिमाही (3 महीने) में बदल सकती हैं। कृपया बैंक या डाकघर से नवीनतम जानकारी पुष्टि कर लें।</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>5 साल की बेटी के लिए **सुकन्या समृद्धि योजना (Sukanya Samriddhi Yojana)** सबसे उपयुक्त सरकारी विकल्प है।
-इसका ब्याज दर वर्तमान में **8.2%** है, जो 1 जुलाई 2026 से लागू है। यह दर हर तिमाही में सरकार द्वारा समीक्षा की जाती है, इसलिए भविष्य में बदलाव हो सकता है।
-इस योजना के मुख्य लाभ:
-* बेटी के लिए लंबे समय तक सुरक्षित निवेश।
-* परिपक्वता पर प्राप्त राशि पर आयकर छूट (Section 80C और 80TTB के तहत)।
-कृपया ध्यान दें: यह जानकारी सामान्य शिक्षा के उद्देश्यों से है। किसी भी योजना में निवेश करने से पहले अपने वित्तीय सलाहकार या CA से अपनी स्थिति के अनुसार पुष्टि अवश्य करें।</t>
+          <t>आपकी बेटी के लिए **सुकन्या समृद्धि योजना (Sukanya Samriddhi Yojana)** सबसे अच्छा विकल्प है।
+यह योजना विशेष रूप से बालिकाओं की शिक्षा और शादी के भविष्य के लिए बनाई गई है:
+* **ब्याज दर:** 8.2% प्रति वर्ष (प्रभावी 1 जुलाई 2026 से)।
+* **लाभ:** यह एक सरकारी योजना है जिसका ब्याज दर सामान्य FD से अधिक होता है और इसमें आयकर की छूट (Section 80C) का लाभ मिलता है।
+**अन्य विकल्प:** आप PPF (Public Provident Fund) भी खोल सकते हैं, जिसकी वर्तमान ब्याज दर 7.1% है। लेकिन बालिकाओं के लिए SSY की दर बेहतर है।
+**ध्यान दें:** छोटी बचत योजनाओं की दरें हर तिमाही (3 महीने) में बदल सकती हैं। कृपया बैंक या डाकघर से नवीनतम जानकारी पुष्टि कर लें।</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>11.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>12.6</v>
+        <v>9.4</v>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
     </row>
@@ -587,14 +587,14 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>1 लाख रुपये की 1 साल की FD मैच्योर होने पर आपको ₹1,06,398.02 मिलेंगे। इसमें ₹6,398.02 ब्याज शामिल है।
-ये रेट SBI के 15 दिसंबर 2025 से लागू हो रहे हैं। ध्यान रखें कि FD पर जो ब्याज मिलता है, वो आपकी आय टैक्स स्लैब के हिसाब से टैक्सेबल होता है।</t>
+          <t>1 लाख रुपये की 1 साल की FD मैच्योर होने पर आपको **₹1,06,398.02** मिलेंगे। इसमें ₹6,398.02 ब्याज शामिल है।
+ये रेट SBI के 15 दिसंबर 2025 से लागू हो रहे हैं। ध्यान रखें कि FD पर जो ब्याज मिलता है, वो आपके टैक्स स्लैब के हिसाब से टैबेबल होता है।</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>1 लाख रुपये की 1 साल की FD मैच्योर होने पर आपको ₹1,06,398.02 मिलेंगे। इसमें ₹6,398.02 ब्याज शामिल है।
-ये रेट SBI के 15 दिसंबर 2025 से लागू हो रहे हैं। ध्यान रखें कि FD पर जो ब्याज मिलता है, वो आपकी आय टैक्स स्लैब के हिसाब से टैक्सेबल होता है।</t>
+          <t>1 लाख रुपये की 1 साल की FD मैच्योर होने पर आपको **₹1,06,398.02** मिलेंगे। इसमें ₹6,398.02 ब्याज शामिल है।
+ये रेट SBI के 15 दिसंबर 2025 से लागू हो रहे हैं। ध्यान रखें कि FD पर जो ब्याज मिलता है, वो आपके टैक्स स्लैब के हिसाब से टैबेबल होता है।</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
     </row>
@@ -636,16 +636,15 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>State Bank of India (SBI) में सेविंग्स अकाउंट पर **2.5%** वार्षिक ब्याज मिलता है।
-यह दर 15 जून 2025 से लागू है। SBI अब बैलेंस की राशि के आधार पर अलग-अलग ब्याज नहीं देता — चाहे खाते में ₹1 हो या ₹1 करोड़, सभी को यह एक ही दर (2.5%) मिलती है।
-ध्यान दें: छोटी वित्त कंपनियाँ (small finance banks) इससे अधिक ब्याज दे सकती हैं, इसलिए SBI की यह दर बाजार में सबसे कम दरों में से एक है।</t>
+          <t>SBI में सेविंग्स अकाउंट पर **2.5% प्रति वर्ष** का ब्याज मिलता है।
+यह दर 15 जून 2025 से लागू है। SBI अब बैलेंस की मात्रा के आधार पर अलग-अलग दरें नहीं देता — चाहे खाते में ₹10 लाख हों या ₹10,000, ब्याज दर समान रहेगी।</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>State Bank of India (SBI) में सेविंग अकाउंट पर **2.5%** प्रतिवर्ष का ब्याज मिलता है।
-यह दर **15 जून 2025** से लागू है। SBI के नियम के अनुसार, खाते में कितनी भी राशि (₹10 लाख या उससे अधिक) क्यों न हो, यह एक ही दर (2.5%) सभी बैलेंस पर लागू होती है।
-ध्यान दें: यह दर SBI की अपनी कार्ड पर दी गई है। छोटी वित्त बैंक (small finance banks) में कभी-कभी इससे अधिक ब्याज मिल सकता है, इसलिए इसे आप एक आधार मान सकते हैं।</t>
+          <t>State Bank of India (SBI) के सेविंग अकाउंट पर **2.50%** प्रतिवर्ष का ब्याज मिलता है।
+यह दर 15 जून, 2025 से लागू है। SBI में अब बैलेंस की मात्रा के आधार पर अलग-अलग ब्याज दरें नहीं होतीं — चाहे खाते में ₹1 हों या ₹1 करोड़, सभी को एक ही दर (2.50%) मिलती है।
+ध्यान दें: यह SBI की अपनी दर है। छोटी वित्त बैंक (Small Finance Banks) अक्सर इससे अधिक ब्याज देती हैं, इसलिए इसे बाजार में मिलने वाली न्यूनतम दर के रूप में देखें।</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -665,14 +664,14 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>NO — lost 1, 1e+07</t>
+          <t>NO — lost 10000, 1e+06</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
     </row>
@@ -687,16 +686,16 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>सबसे सस्ता बीमा विकल्प **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY)** है, जिसका वार्षिक प्रीमियम केवल **₹20** है।
-ध्यान रखें: PMSBY में कवरेज सिर्फ़ **अकस्मात मृत्यु या अक्षमता** (accidental death/disability) तक सीमित है — बीमारी से होने वाली मृत्यु इसमें शामिल नहीं है।
-यदि आप किसी भी कारण से मृत्यु का कवरेज चाहते हैं, तो **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY)** लें, जिसका प्रीमियम **₹436** प्रति वर्ष है।</t>
+          <t>सबसे सस्ता बीमा **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY)** है, जिसका प्रीमियम सिर्फ ₹20 प्रति वर्ष है।
+ध्यान दें: PMSBY में केवल **दुर्घटना से मृत्यु या अपंगता** की कवरेज होती है, बीमारी से मृत्यु नहीं।
+अगर आपको बीमारी सहित किसी भी कारण से मृत्यु का खतरा है, तो **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY)** लें, जिसका प्रीमियम ₹436 प्रति वर्ष है।</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>सबसे सस्ता बीमा विकल्प **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY)** है, जिसका वार्षिक प्रीमियम केवल **₹20** है।
-ध्यान रखें: PMSBY में कवरेज सिर्फ़ **अकस्मात मृत्यु या अक्षमता** (accidental death/disability) तक सीमित है — बीमारी से होने वाली मृत्यु इसमें शामिल नहीं है।
-यदि आप किसी भी कारण से मृत्यु का कवरेज चाहते हैं, तो **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY)** लें, जिसका प्रीमियम **₹436** प्रति वर्ष है।</t>
+          <t>सबसे सस्ता बीमा **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY)** है, जिसका प्रीमियम सिर्फ ₹20 प्रति वर्ष है।
+ध्यान दें: PMSBY में केवल **दुर्घटना से मृत्यु या अपंगता** की कवरेज होती है, बीमारी से मृत्यु नहीं।
+अगर आपको बीमारी सहित किसी भी कारण से मृत्यु का खतरा है, तो **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY)** लें, जिसका प्रीमियम ₹436 प्रति वर्ष है।</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
     </row>
@@ -738,16 +737,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PPF का पूरा नाम Public Provident Fund है। यह सरकार द्वारा संचालित एक लंबी अवधि की बचत योजना है जिसमें आप हर साल निवेश कर सकते हैं।
-इसमें आपको **7.10%** प्रतिवर्ष का ब्याज मिलता है।
-ध्यान दें: यह दर 1 जुलाई 2026 से लागू हुई थी और सरकार हर तिमाही में इन दरों की समीक्षा करती है, इसलिए भविष्य में यह बदल सकती है।</t>
+          <t>PPF (Public Provident Fund) एक सरकारी द्वारा समर्थित लॉन्ग-टर्म बचत योजना है। इसमें आप न्यूनतम 1 वर्ष के लिए निवेश करते हैं, लेकिन पूरा टर्म 15 साल होता है।
+इस पर **7.1%** की दर से ब्याज मिलता है। यह दर Ministry of Finance द्वारा हर क्वार्टर (3 महीने) में अपडेट की जाती है।
+**महत्वपूर्ण जानकारी:**
+- **Effective Rate Date:** 1 July 2026 से लागू।
+- **Source:** Ministry of Finance (Department of Economic Affairs).
+- **Note:** चूंकि छोटी बचत दरें हर क्वार्टर बदल सकती हैं, इसलिए नवीनतम जानकारी के लिए nsiindia.gov.in या अपने बैंक से पुष्टि कर लें।</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PPF का पूरा नाम Public Provident Fund है। यह सरकार द्वारा संचालित एक लंबी अवधि की बचत योजना है जिसमें आप हर साल निवेश कर सकते हैं।
-इसमें आपको **7.10%** प्रतिवर्ष का ब्याज मिलता है।
-ध्यान दें: यह दर 1 जुलाई 2026 से लागू हुई थी और सरकार हर तिमाही में इन दरों की समीक्षा करती है, इसलिए भविष्य में यह बदल सकती है।</t>
+          <t>PPF (Public Provident Fund) एक सरकारी द्वारा समर्थित लॉन्ग-टर्म बचत योजना है। इसमें आप न्यूनतम 1 वर्ष के लिए निवेश करते हैं, लेकिन पूरा टर्म 15 साल होता है।
+इस पर **7.1%** की दर से ब्याज मिलता है। यह दर Ministry of Finance द्वारा हर क्वार्टर (3 महीने) में अपडेट की जाती है।
+**महत्वपूर्ण जानकारी:**
+- **Effective Rate Date:** 1 July 2026 से लागू।
+- **Source:** Ministry of Finance (Department of Economic Affairs).
+- **Note:** चूंकि छोटी बचत दरें हर क्वार्टर बदल सकती हैं, इसलिए नवीनतम जानकारी के लिए nsiindia.gov.in या अपने बैंक से पुष्टि कर लें।</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -771,10 +776,10 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
     </row>
@@ -789,50 +794,20 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>आपकी उम्र (62 वर्ष) के आधार पर आप 'सीनियर सिटीजन' श्रेणी में आते हैं। सरकार द्वारा चलाए जाने वाले छोटे बचत योजनाओं (Small Savings Schemes) का ब्याज दर आम FD से अधिक है, इसलिए वे आपके लिए बेहतर विकल्प हो सकते हैं।
-यहाँ 62 वर्षीय व्यक्ति के लिए उपलब्ध प्रमुख विकल्प और उनके वर्तमान ब्याज दर दिए गए हैं:
-1. **सीनियर सिटीजन सेविंग्स स्कीम (SCSS)**
-   - **ब्याज दर:** 8.2% प्रति वर्ष
-   - **स्रोत:** वित्त मंत्रालय (आर्थिक कार्य विभाग)
-   - **प्रभावी तिथि:** 1 जुलाई 2026 से
-   - **विशेषता:** यह योजना विशेष रूप से सीनियर सिटीजन के लिए है। ब्याज दरें हर तिमाही में संशोधित की जा सकती हैं, इसलिए अगली तिमाही (1 अक्टूबर 2026) में रेट बदल सकता है।
-2. **राष्ट्रीय बचत प्रमाणपत्र (NSC)**
-   - **ब्याज दर:** 7.7% प्रति वर्ष
-   - **स्रोत:** वित्त मंत्रालय (आर्थिक कार्य विभाग)
-   - **प्रभावी तिथि:** 1 जुलाई 2026 से
-   - **विशेषता:** यह एक लॉन्ग-टर्म निवेश है। SCSS की तुलना में इसकी बचत दर थोड़ी कम है, लेकिन यह भी सुरक्षित विकल्प है।
-3. **बैंक FD (सिनियर सिटीजन रेट)**
-   - **उदाहरण के लिए SBI:** 1 वर्ष की अवधि के लिए 6.75% प्रति वर्ष
-   - **स्रोत:** State Bank of India
-   - **प्रभावी तिथि:** 15 दिसंबर 2025 से
-   - **विशेषता:** SBI में 60 वर्ष और उससे अधिक उम्र के ग्राहकों को बेस रेट पर 0.5% का बोनस मिलता है।
-**निष्कर्ष:**
-अगर आपका मुख्य उद्देश्य नियमित और उच्च इनकम है, तो **SCSS (8.2%)** वर्तमान में सबसे अच्छा विकल्प प्रतीत होता है क्योंकि इसकी ब्याज दर NSC (7.7%) और SBI FD (6.75%) दोनों से अधिक है।
-ध्यान दें: छोटी बचत योजनाओं की दरें हर तिमाही में बदल सकती हैं, इसलिए निवेश करने से पहले नवीनतम रेट की पुष्टि अवश्य करें।</t>
+          <t>62 साल की उम्र में आप सीनियर सिटीजन के तहत बेहतर ब्याज दरें पा सकते हैं। यहाँ कुछ विकल्प दिए गए हैं:
+1. **बैंक FD (सावधि जमा):** SBI जैसे बैंकों में 12 महीने की FD पर सीनियर सिटीजन को 6.75% प्रति वर्ष मिलते हैं। यह दर 15 दिसंबर 2025 से लागू है।
+2. **सरकारी स्कीम (सीनियर सिटीजन सेविंग्स स्कीम - SCSS):** यह स्कीम विशेष रूप से सीनियर सिटीजनों के लिए है और इसमें वर्तमान में 8.2% की दर मिलती है।
+3. **पोस्ट ऑफिस मंथली इनकम स्कीम (POMIS):** अगर आपको हर महीने नियमित आय चाहिए, तो यह स्कीम अच्छा विकल्प हो सकता है, जिसमें वर्तमान में 7.4% की दर है।
+**ध्यान दें:** सरकारी स्कीमों की दरें हर तिमाही (3 महीने) में बदल सकती हैं। कृपया किसी भी निवेश से पहले अपनी नजदीकी बैंक या पोस्ट ऑफिस से पुष्टि कर लें।</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>आपकी उम्र (62 वर्ष) के आधार पर आप 'सीनियर सिटीजन' श्रेणी में आते हैं। सरकार द्वारा चलाए जाने वाले छोटे बचत योजनाओं (Small Savings Schemes) का ब्याज दर आम FD से अधिक है, इसलिए वे आपके लिए बेहतर विकल्प हो सकते हैं।
-यहाँ 62 वर्षीय व्यक्ति के लिए उपलब्ध प्रमुख विकल्प और उनके वर्तमान ब्याज दर दिए गए हैं:
-1. **सीनियर सिटीजन सेविंग्स स्कीम (SCSS)**
-   - **ब्याज दर:** 8.2% प्रति वर्ष
-   - **स्रोत:** वित्त मंत्रालय (आर्थिक कार्य विभाग)
-   - **प्रभावी तिथि:** 1 जुलाई 2026 से
-   - **विशेषता:** यह योजना विशेष रूप से सीनियर सिटीजन के लिए है। ब्याज दरें हर तिमाही में संशोधित की जा सकती हैं, इसलिए अगली तिमाही (1 अक्टूबर 2026) में रेट बदल सकता है।
-2. **राष्ट्रीय बचत प्रमाणपत्र (NSC)**
-   - **ब्याज दर:** 7.7% प्रति वर्ष
-   - **स्रोत:** वित्त मंत्रालय (आर्थिक कार्य विभाग)
-   - **प्रभावी तिथि:** 1 जुलाई 2026 से
-   - **विशेषता:** यह एक लॉन्ग-टर्म निवेश है। SCSS की तुलना में इसकी बचत दर थोड़ी कम है, लेकिन यह भी सुरक्षित विकल्प है।
-3. **बैंक FD (सिनियर सिटीजन रेट)**
-   - **उदाहरण के लिए SBI:** 1 वर्ष की अवधि के लिए 6.75% प्रति वर्ष
-   - **स्रोत:** State Bank of India
-   - **प्रभावी तिथि:** 15 दिसंबर 2025 से
-   - **विशेषता:** SBI में 60 वर्ष और उससे अधिक उम्र के ग्राहकों को बेस रेट पर 0.5% का बोनस मिलता है।
-**निष्कर्ष:**
-अगर आपका मुख्य उद्देश्य नियमित और उच्च इनकम है, तो **SCSS (8.2%)** वर्तमान में सबसे अच्छा विकल्प प्रतीत होता है क्योंकि इसकी ब्याज दर NSC (7.7%) और SBI FD (6.75%) दोनों से अधिक है।
-ध्यान दें: छोटी बचत योजनाओं की दरें हर तिमाही में बदल सकती हैं, इसलिए निवेश करने से पहले नवीनतम रेट की पुष्टि अवश्य करें।</t>
+          <t>62 साल की उम्र में आप सीनियर सिटीजन के तहत बेहतर ब्याज दरें पा सकते हैं। यहाँ कुछ विकल्प दिए गए हैं:
+1. **बैंक FD (सावधि जमा):** SBI जैसे बैंकों में 12 महीने की FD पर सीनियर सिटीजन को 6.75% प्रति वर्ष मिलते हैं। यह दर 15 दिसंबर 2025 से लागू है।
+2. **सरकारी स्कीम (सीनियर सिटीजन सेविंग्स स्कीम - SCSS):** यह स्कीम विशेष रूप से सीनियर सिटीजनों के लिए है और इसमें वर्तमान में 8.2% की दर मिलती है।
+3. **पोस्ट ऑफिस मंथली इनकम स्कीम (POMIS):** अगर आपको हर महीने नियमित आय चाहिए, तो यह स्कीम अच्छा विकल्प हो सकता है, जिसमें वर्तमान में 7.4% की दर है।
+**ध्यान दें:** सरकारी स्कीमों की दरें हर तिमाही (3 महीने) में बदल सकती हैं। कृपया किसी भी निवेश से पहले अपनी नजदीकी बैंक या पोस्ट ऑफिस से पुष्टि कर लें।</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -856,10 +831,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15.9</v>
+        <v>14.9</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
     </row>
@@ -874,21 +849,36 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SBI में बचत खाता खोलने के लिए आपको तीन चीज़ें जमा करनी होंगी:
-1. **पते और नाम का सबूत (OVD):** इनमें से कोई एक — आधार कार्ड, वोटर आईडी, NREGA जॉब कार्ड, या नेशनल पॉपुलेशन रजिस्टर का लेटर।
-2. **आयकर पहचान:** PAN कार्ड। अगर आपके पास PAN नहीं है, तो फॉर्म 60 भरना होगा।
-3. **व्यक्तिगत जानकारी:** आपका फोटो और हस्ताक्षर।
-**ध्यान दें:** अगर आपके पास ऊपर दी गई कोई भी KYC दस्तावेज़ नहीं है, तो SBI आपको एक 'Small Account' खोलकर दे सकता है। इसमें शुरुआत में राशि सीमित (₹50,000 से अधिक बैलेंस नहीं) होती है, लेकिन आप बाद में पूरा KYC करके इसे सामान्य खाते में बदल सकते हैं।</t>
+          <t>SBI में बचत खाता खोलने के लिए आपको दो मुख्य दस्तावेज़ों की आवश्यकता होगी:
+1. **पते और नाम का सबूत (Proof of Name &amp; Address):** आप इनमें से कोई एक Officially Valid Document (OVD) दे सकते हैं:
+   - आधार कार्ड (Aadhaar)
+   - वोटर आईडी (Voter ID)
+   - NREGA जॉब कार्ड
+   - नेशनल पॉपुलेशन रजिस्टर (NPR) से प्राप्त पत्र
+2. **आयकर पहचान (Tax Identification):**
+   - PAN कार्ड, या
+   - यदि आपके पास PAN नहीं है, तो **फॉर्म 60**।
+**ध्यान दें:**
+- RBI के नियमों के अनुसार, आपको बस एक OVD और PAN/फॉर्म 60 की जरूरत है (RBI FAQ)।
+- SBI के Basic Savings Bank Deposit Account (BSBD) के लिए न्यूनतम बैलेंस शून्य होता है, लेकिन यदि आपके पास उपरोक्त दस्तावेज़ नहीं हैं, तो आप 'Small Account' खोल सकते हैं जिसमें सीमाएँ होती हैं।
+आप इन दस्तावेज़ों के साथ निकटतम SBI शाखा में जाकर खाता खोल सकते हैं।</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SBI में बचत खाता खोलने के लिए आपको तीन चीज़ें जमा करनी होंगी:
-1. **पहचान और पता साबित करने वाला दस्तावेज़ (OVD):** इनमें से कोई एक — आधार कार्ड, वोटर आईडी, या NREGA जॉब कार्ड।
-2. **आयकर पहचान (PAN):** अपना PAN कार्ड या Form 60 (अगर आपके पास PAN नहीं है)।
-3. **व्यापार/वित्तीय स्थिति:** अगर खाता किसी व्यापार के लिए है, तो उससे जुड़े दस्तावेज़।
-**ध्यान दें:** अगर आपके पास ऊपर दिए गए कोई भी KYC दस्तावेज़ नहीं हैं, तो आप SBI में एक 'Small Account' खोल सकते हैं। इसमें आपको 50,000 रुपये से ज़्यादा बैलेंस नहीं रखना है और महीने में सिर्फ 10,000 रुपये ही निकालने हैं। जब तक आप पूरा KYC नहीं करते, यह खाता तभी तक चलता है।
-अगर आप एक 'Basic Savings Bank Deposit Account' (BSBD) खोलते हैं, तो उसमें कोई न्यूनतम बैलेंस रखने की ज़रूरत नहीं है, लेकिन इस शर्त पर कि आपके पास SBI में कोई दूसरा आम बचत खाता नहीं होना चाहिए।</t>
+          <t>SBI में बचत खाता खोलने के लिए आपको मुख्य रूप से दो तरह के दस्तावेज़ चाहिए:
+1. **पते और नाम का सबूत (Proof of Name &amp; Address):** आप इनमें से कोई एक Officially Valid Document (OVD) दे सकते हैं:
+   - आधार कार्ड (Aadhaar)
+   - वोटर आईडी (Voter ID)
+   - NREGA जॉब कार्ड
+   - नेशनल पॉपुलेशन रजिस्टर (NPR) का लेटर
+2. **आयकर के लिए सबूत:**
+   - PAN कार्ड, या
+   - अगर आपके पास PAN नहीं है, तो फॉर्म 60 (Form 60)
+**ध्यान दें:**
+- RBI के नियमों के अनुसार, आपका पुराना खाता खोलने के लिए ये दस्तावेज़ काफी हैं।
+- अगर आप Basic Savings Bank Deposit Account (BSBD) खोल रहे हैं जो कि जीरो बैलेंस अकाउंट है, तो भी ये KYC दस्तावेज़ जरूरी होंगे।
+- अगर आपके पास कोई Officially Valid Document नहीं है, तो SBI 'Small Account' के तहत एक सीमित खाता खोल सकता है, लेकिन उसमें राशि और लेनदेन की सीमाएं होती हैं।</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -912,10 +902,10 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
     </row>
@@ -930,17 +920,15 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>अगर बैंक डूब जाता है, तो आपका पैसा **₹5,00,000** तक सुरक्षित है।
-यह कवरेज RBI के तहत DICGC (Deposit Insurance and Credit Guarantee Corporation) द्वारा दिया गया है। इसमें आपके मूल धन राशि और उस पर लगा ब्याज दोनों शामिल हैं।
-ध्यान रखें: एक ही बैंक में आपकी सभी जमा राशियाँ (सभी शाखाओं की) जोड़कर ₹5 लाख का कवरेज लागू होता है। अगर आपके पास ₹5 लाख से ज्यादा पैसे हैं, तो बाकी राशि सुरक्षित नहीं मानी जाएगी।
+          <t>अगर आपका बैंक डूब जाता है, तो डिपॉजिट इन्श्योरेंस एंड गारंटी कॉर्पोरेशन ऑफ इंडिया (DICGC) के तहत **₹5,00,000** तक का पैसा सुरक्षित होता है।
+यह राशि आपके मूल धन और उस पर जुड़े ब्याज दोनों को मिलकर ढकती है। यह कवरेज हर बैंक में अलग-अलग शाखाओं में रखी गई सारी जमा राशियों को जोड़कर लागू होता है, न कि प्रति व्यक्ति या प्रति खाता।
 स्रोत: RBI FAQ — Deposit Insurance (DICGC)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>अगर बैंक डूब जाता है, तो आपका पैसा **₹5,00,000** तक सुरक्षित है।
-यह कवरेज RBI के तहत DICGC (Deposit Insurance and Credit Guarantee Corporation) द्वारा दिया गया है। इसमें आपके मूल धन राशि और उस पर लगा ब्याज दोनों शामिल हैं।
-ध्यान रखें: एक ही बैंक में आपकी सभी जमा राशियाँ (सभी शाखाओं की) जोड़कर ₹5 लाख का कवरेज लागू होता है। अगर आपके पास ₹5 लाख से ज्यादा पैसे हैं, तो बाकी राशि सुरक्षित नहीं मानी जाएगी।
+          <t>अगर आपका बैंक डूब जाता है, तो डिपॉजिट इन्श्योरेंस एंड गारंटी कॉर्पोरेशन ऑफ इंडिया (DICGC) के तहत **₹5,00,000** तक का पैसा सुरक्षित होता है।
+यह राशि आपके मूल धन और उस पर जुड़े ब्याज दोनों को मिलकर ढकती है। यह कवरेज हर बैंक में अलग-अलग शाखाओं में रखी गई सारी जमा राशियों को जोड़कर लागू होता है, न कि प्रति व्यक्ति या प्रति खाता।
 स्रोत: RBI FAQ — Deposit Insurance (DICGC)</t>
         </is>
       </c>
@@ -965,10 +953,10 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>8.9</v>
+        <v>10.8</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
     </row>
@@ -983,45 +971,35 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>जीरो बैलेंस खाता वह है जिसमें आपको न्यूनतम बैलेंस रखने की जरूरत नहीं होती। भारत में इसका मतलब आमतौर पर दो अलग-अलग खातों से है, और कौन खोल सकता है, यह इस बात पर निर्भर करता है कि आपके पास KYC (पहचान) के कागजात हैं या नहीं:
-1. **Basic Savings Bank Deposit Account (BSBD)**
-   - **कौन खोल सकता है:** कोई भी व्यक्ति, बशर्ते उसके पास मान्य KYC दस्तावेज हों।
-   - **विशेषता:** यह पूरी तरह से KYC-अनुपालन खाता है।
-   - **महत्वपूर्ण शर्त (SBI नियम के अनुसार):** आप BSBD खोल सकते हैं, लेकिन यदि आपके पास पहले से कोई अन्य Savings Bank Account है, तो आपको उसे 30 दिनों के भीतर बंद करना होगा। एक समय में केवल एक ही BSBD खाता रखा जा सकता है।
-2. **Small Account (Limited KYC)**
-   - **कौन खोल सकता है:** 18 वर्ष से ऊपर का कोई भी व्यक्ति जो Officially Valid KYC दस्तावेज प्रस्तुत नहीं कर पा रहा है।
-   - **शर्तें:** इसमें बैलेंस ₹50,000 तक हो सकता है और माह में कुल निकासी/ट्रांसफर ₹10,000 तक सीमित है। यदि आप बाद में KYC दस्तावेज जमा कराते हैं, तो इसे नियमित Savings Account में बदला जा सकता है।
-**आवश्यक दस्तावेज (KYC के लिए):**
-RBI के निर्देशों के अनुसार, खाता खोलने के लिए आपको निम्नलिखित में से एक Officially Valid Document (OVD) की जरूरत होगी:
-- Aadhaar नंबर का प्रमाण
-- वोटर आईडी कार्ड
-- NREGA जॉब कार्ड
-- राष्ट्रीय जनगणना रजिस्टर द्वारा जारी पत्र
-इसके अलावा, आपका नाम और पता साबित करने के लिए PAN कार्ड (या यदि PAN नहीं है तो Form 60) की आवश्यकता होगी।</t>
+          <t>जीरो बैलेंस खाता वह है जिसमें न्यूनतम बैलेंस रखने की जरूरत नहीं होती। भारत में मुख्य रूप से दो तरह के जीरो बैलेंस खाते मिलते हैं:
+1. **प्रधानमंत्री जन-धन योजना (PMJDY):** यह सरकार का राष्ट्रीय कार्यक्रम है। इसमें कोई न्यूनतम बैलेंस नहीं रखना होता, और इस पर ब्याज भी मिलता है।
+2. **बेसिक सेविंग्स बैंक डिपॉजिट (BSBD) खाता:** सभी सरकारी और निजी बैंक इसे खोलते हैं। यह भी जीरो बैलेंस वाला खाता है, लेकिन इसमें चेकबुक नहीं मिलती और माह में 4 बार तक निकासी मुफ्त होती है।
+**कौन खोल सकता है?**
+- **PMJDY:** कोई भी व्यक्ति जो पहले से बैंक में खाता नहीं रखता, उसे यह खाता खोलने का अधिकार है।
+- **BSBD:** किसी भी भारतीय नागरिक को खुद के नाम पर या किसी अल्पवयस्क (minor) के लिए यह खाता खोल सकते हैं, बशर्ते उनके पास मान्य KYC दस्तावेज हों।
+**जरूरी शर्तें:**
+- BSBD खाता रखने वाले व्यक्ति को दूसरा कोई सेविंग्स बैंक खाता नहीं होना चाहिए। अगर पहले से खाता है, तो उसे 30 दिनों में बंद करना होगा।
+- खाता खोलने के लिए आधार कार्ड, वोटर्स आईडी, या फॉर्म 60 (यदि PAN न हो) जैसे आधिकारिक दस्तावेज चाहिए होंगे।</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>जीरो बैलेंस खाता वह है जिसमें आपको न्यूनतम बैलेंस रखने की जरूरत नहीं होती और इस पर कोई मेंटेनेंस चार्ज नहीं लगता। यह मुख्य रूप से दो तरह के होते हैं:
-1. **बेसिक सेविंग्स बैंक डिपॉजिट (BSBD) खाता**: यह RBI के नियमों के तहत हर किसी को खुलवाया जा सकता है। इसमें न्यूनतम बैलेंस शून्य होता है, लेकिन आप एक ही समय में केवल एक BSBD खाता रख सकते हैं और यदि आपके पास पहले से कोई सामान्य सेविंग्स अकाउंट है तो उसे बंद करना होगा।
-2. **प्रधानमंत्री जन धन योजना (PMJDY)**: यह सरकार की एक पहल है जो हर नागरिक को जीरो बैलेंस खाता खोलने और ₹10,000 तक का ओवरड्राफ्ट सुविधा प्रदान करने के लिए प्रोत्साहित करती है।
-**कागजात (KYC) की आवश्यकता:**
-खाता खोलने के लिए KYC अनिवार्य है। आपको निम्नलिखित दस्तावेजों में से एक या अधिक देना होगा:
-- आधार कार्ड
-- वोटर्स आईडी
-- NREGA जॉब कार्ड
-- नेशनल पॉपुलेशन रजिस्टर (NPR) का पत्र
-- PAN कार्ड (या यदि PAN नहीं है तो फॉर्म 60)</t>
+          <t>जीरो बैलेंस खाता वह है जिसमें आपको कोई न्यूनतम बैलेंस रखने की जरूरत नहीं होती और न ही महीने में कोई चार्ज कटेगा।
+**कौन खोल सकता है?**
+RBI के नियमों के अनुसार, किसी भी व्यक्ति को Basic Savings Bank Deposit (BSBD) खाता खोलने का अधिकार है। इसके लिए आपको सिर्फ एक Officially Valid Document (OVD) जैसे आधार कार्ड या वोटर आईडी और Form 60 (यदि आपका PAN नहीं है) की जरूरत होगी।
+**ध्यान रखें:**
+1. **एक ही बैंक में:** RBI के नियम के अनुसार, एक व्यक्ति किसी भी एक बैंक में केवल एक BSBD खाता ही रख सकता है। अगर आपके पास पहले से उसी बैंक में कोई सामान्य सेविंग अकाउंट है, तो आपको उसे बंद करना होगा या फिर दूसरे बैंक में यह खाता खोलना होगा।
+2. **PMJDY:** यदि आप प्रधानमंत्री जन-धन योजना के तहत खाता खोल रहे हैं, तो इसमें कोई न्यूनतम बैलेंस नहीं है और इसमें रुपा डेबिट कार्ड भी मुफ्त मिलता है।</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>docs.search, india.get_scheme_details</t>
+          <t>docs.search</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>docs.search, india.get_scheme_details</t>
+          <t>docs.search</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1031,14 +1009,14 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>NO — lost 18, 30, 50000</t>
+          <t>NO — lost 4, 30</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15.2</v>
+        <v>13.6</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15.4</v>
+        <v>14.2</v>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
     </row>
@@ -1053,20 +1031,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,000 रुपये की सैलरी के लिए आप पैसों को इस तरह बांट सकते हैं:
-• **आवश्यक खर्च (Needs): ₹15,000** — किराया, भोजन, बिल और यातायात जैसे जरूरी खर्च।
-• **चाहें (Wants): ₹9,000** — मूवीज, शॉपिंग, दोस्तों के साथ घूमना आदि मनोरंजन के लिए।
-• **बचत (Savings): ₹6,000** — यह वह राशि है जो आप भविष्य के लिए जमा करेंगे।
-सबसे पहले एक Emergency Fund (आपातकालीन निधि) बनाएं जिसमें कम से कम 3-6 महीने का खर्च शामिल हो। उसके बाद आप इसे FD, Mutual Funds या अन्य विकल्पों में लगा सकते हैं।</t>
+          <t>₹30,000 की सैलरी पर पैसों को तीन हिस्सों में बाँटना सबसे समझदारी है:
+1. **जरूरतें (Needs) — ₹15,000:** घर का किराया, खाना, बिल और यात्रा जैसे जरूरी खर्च।
+2. **चाहें (Wants) — ₹9,000:** शौक, बाहर खाना, शॉपिंग आदि के लिए।
+3. **बचत (Savings) — ₹6,000:** यह वो पैसे हैं जो आप भविष्य के लिए जमा करेंगे।
+**शुरुआत में क्या करें?**
+- सबसे पहले एक **Emergency Fund** बनाएँ। कम से कम 3 महीने के खर्च (लगभग ₹45,000) को एक अलग बैंक खाते में रखें।
+- बची हुई बचत को आप FD या Mutual Fund (SIP) में लगा सकते हैं।</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>₹30,000 की सैलरी पर पैसा कैसे बाँटना है, इसका एक सिंपल फॉर्मूला है:
-1. **जरूरतें (Needs): ₹15,000** — रेंट, खाना, बिजली का बिल, यात्रा। ये वो पैसे हैं जो बिना नहीं रह सकते।
-2. **चाहें (Wants): ₹9,000** — मूवी, बाहर खाना, शॉपिंग। इसमें थोड़ी लचीलापन रखें।
-3. **बचत (Savings): ₹6,000** — यह वो पैसे हैं जो आप भविष्य के लिए जमा करेंगे।
-सबसे पहले एक Emergency Fund (आपातकालीन निधि) बनाएं जिसमें कम से कम 3-6 महीने का खर्च आ जाए। उसके बाद आप SIP या FD जैसे विकल्पों पर विचार कर सकते हैं।</t>
+          <t>₹30,000 की सैलरी पर आप 50-30-20 नियम का उपयोग कर सकते हैं। इसका मतलब है कि आपकी राशि को तीन हिस्सों में बाँटा जाए:
+1. **आवश्यकताएँ (Needs): ₹15,000** — इसमें किराया, खाना, बिजली का बिल और अन्य जरूरी खर्च शामिल हैं।
+2. **इच्छाएँ (Wants): ₹9,000** — यह आपकी मनोरंजन, शॉपिंग या बाहर खाने जैसे वैयक्तिक खर्चों के लिए है।
+3. **बचत (Savings): ₹6,000** — इस राशि को निवेश या बचत के लिए अलग रखें।
+ध्यान दें कि यह गणना आपकी टैक्स-पश्चात (take-home) सैलरी पर आधारित है।</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1084,16 +1064,16 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>NO — lost 45000</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>13.1</v>
+        <v>9</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>13.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
     </row>
@@ -1108,15 +1088,14 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SBI के होम लोन पर ब्याज दरें **₹7.25% से शुरू** होती हैं।
-हालाँकि, ध्यान रखें कि ये दरें केवल शुरुआती (starting) दरें हैं। आपकी वास्तविक ब्याज दर आपकी क्रेडिट स्कोर और प्रोफाइल पर निर्भर करेगी, जो आमतौर पर इनसे अधिक हो सकती है।
-ये दरें **1 अप्रैल 2026** से लागू हैं।</t>
+          <t>State Bank of India (SBI) के होम लोन पर ब्याज दर **7.25% से शुरू** होती है।
+यह दर प्रभावी **1 अप्रैल 2026** से लागू है। ध्यान रखें कि यह 'शुरुआती' दर है — आपकी वास्तविक दर आप के CIBIL स्कोर और अन्य वित्तीय स्थिति पर निर्भर करेगी।</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>State Bank of India की वर्तमान होम लोन ब्याज दरें **7.25% से शुरू होकर 8.45%** तक हैं।
-ये दरें 1 अप्रैल 2026 से लागू हैं। ध्यान रखें कि ये 'शुरू होने वाली' दरें हैं — आपकी व्यक्तिगत दर आपकी क्रेडिट स्कोर और अन्य प्रोफाइल के आधार पर इससे अलग हो सकती है।</t>
+          <t>State Bank of India के अनुसार होम लोन पर ब्याज दर **7.25% से शुरू** होती है।
+ध्यान दें: ये दरें 1 अप्रैल 2026 से लागू हैं और केवल शुरुआती दरें हैं। आपकी वास्तविक ब्याज दर आपकी क्रेडिट स्कोर और अन्य प्रोफाइल पर निर्भर करेगी, जो कि विज्ञापित दर से अधिक हो सकती है।</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1140,10 +1119,10 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
     </row>
@@ -1158,30 +1137,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>बुढ़ापे के लिए पेंशन का इंतज़ाम करने के लिए सरकार की सबसे सीधी स्कीम **अटल पेंशन योजना (APY)** है।
-**अटल पेंशन योजना (APY) कैसे काम करती है:**
-- आप 60 साल की उम्र से हर महीने तयशुदा पेंशन पाएंगे।
-- पेंशन के विकल्प: ₹1,000, ₹2,000, ₹3,000, ₹4,000 या ₹5,000 प्रति माह।
-- जो राशि आपको हर महीने जमा करनी होगी, वह आपकी **उम्र** और चुनी गई पेंशन पर निर्भर करती है। किसी एक निश्चित राशि का दावा नहीं किया जा सकता क्योंकि यह उम्र के साथ बदलता है।
-**अतिरिक्त सुरक्षा (बीमा):**
-पेंशन के साथ-साथ आपकी आर्थिक सुरक्षा के लिए ये दो योजनाएं भी देख सकते हैं:
-1. **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY):** सालाना ₹436 का प्रीमियम देकर ₹2,00,000 का जीवन बीमा मिलता है (किसी भी कारण मृत्यु पर)।
-2. **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY):** सालाना ₹20 का प्रीमियम देकर ₹2,00,000 का बीमा मिलता है (केवल दुर्घटनाजनित मृत्यु और अक्षमता पर, बीमारी से नहीं)।
-इन योजनाओं के लिए आप अपने बैंक या डाक घर में जाकर अपना खाता जोड़ सकते हैं।</t>
+          <t>बुढ़ापे की सुरक्षा के लिए सरकार की कई स्कीमें हैं। आप अपनी उम्र और जरूरत के हिसाब से चुन सकते हैं:
+1. अटल पेंशन योजना (APY): यह सीधे बुढ़ापे के लिए है। आप 60 साल की उम्र तक माहिर ₹1,000 से ₹5,000 का पेंशन चुन सकते हैं। इसका योगदान आपकी वर्तमान उम्र पर निर्भर करता है, इसलिए सटीक राशि जानने के लिए अपने बैंक से संपर्क करें।
+2. प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY): यह मृत्यु के दौरान परिवार को ₹2 लाख का सुरक्षा कवरेज देती है। इसका वार्षिक प्रीमियम ₹436 है। ध्यान रहे, यह सिर्फ मौत के लिए है, बीमारी के लिए नहीं।
+3. प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY): यह दुर्घटना में मृत्यु या स्थायी अक्षमता के लिए कवरेज देती है। इसका वार्षिक प्रीमियम ₹20 है।
+4. सीनियर सिटीजन सेविंग्स स्कीम (SCSS): यदि आप 60 साल या उससे अधिक उम्र के हैं, तो यह एक अच्छा विकल्प है क्योंकि इसमें ब्याज दरें आम निवेशकों की तुलना में अधिक होती हैं।
+5. पॉस्ट ऑफिस मंथली इनकम स्कीम (POMIS): यदि आपको नियमित मासिक आय चाहिए, तो यह स्कीम उपयुक्त हो सकती है।</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>बुढ़ापे के लिए पेंशन का इंतज़ाम करने के लिए सरकार की सबसे सीधी स्कीम **अटल पेंशन योजना (APY)** है।
-**अटल पेंशन योजना (APY) कैसे काम करती है:**
-- आप 60 साल की उम्र से हर महीने तयशुदा पेंशन पाएंगे।
-- पेंशन के विकल्प: ₹1,000, ₹2,000, ₹3,000, ₹4,000 या ₹5,000 प्रति माह।
-- जो राशि आपको हर महीने जमा करनी होगी, वह आपकी **उम्र** और चुनी गई पेंशन पर निर्भर करती है। किसी एक निश्चित राशि का दावा नहीं किया जा सकता क्योंकि यह उम्र के साथ बदलता है।
-**अतिरिक्त सुरक्षा (बीमा):**
-पेंशन के साथ-साथ आपकी आर्थिक सुरक्षा के लिए ये दो योजनाएं भी देख सकते हैं:
-1. **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY):** सालाना ₹436 का प्रीमियम देकर ₹2,00,000 का जीवन बीमा मिलता है (किसी भी कारण मृत्यु पर)।
-2. **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY):** सालाना ₹20 का प्रीमियम देकर ₹2,00,000 का बीमा मिलता है (केवल दुर्घटनाजनित मृत्यु और अक्षमता पर, बीमारी से नहीं)।
-इन योजनाओं के लिए आप अपने बैंक या डाक घर में जाकर अपना खाता जोड़ सकते हैं।</t>
+          <t>बुढ़ापे की सुरक्षा के लिए सरकार की कई स्कीमें हैं। आप अपनी उम्र और जरूरत के हिसाब से चुन सकते हैं:
+1. अटल पेंशन योजना (APY): यह सीधे बुढ़ापे के लिए है। आप 60 साल की उम्र तक माहिर ₹1,000 से ₹5,000 का पेंशन चुन सकते हैं। इसका योगदान आपकी वर्तमान उम्र पर निर्भर करता है, इसलिए सटीक राशि जानने के लिए अपने बैंक से संपर्क करें।
+2. प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY): यह मृत्यु के दौरान परिवार को ₹2 लाख का सुरक्षा कवरेज देती है। इसका वार्षिक प्रीमियम ₹436 है। ध्यान रहे, यह सिर्फ मौत के लिए है, बीमारी के लिए नहीं।
+3. प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY): यह दुर्घटना में मृत्यु या स्थायी अक्षमता के लिए कवरेज देती है। इसका वार्षिक प्रीमियम ₹20 है।
+4. सीनियर सिटीजन सेविंग्स स्कीम (SCSS): यदि आप 60 साल या उससे अधिक उम्र के हैं, तो यह एक अच्छा विकल्प है क्योंकि इसमें ब्याज दरें आम निवेशकों की तुलना में अधिक होती हैं।
+5. पॉस्ट ऑफिस मंथली इनकम स्कीम (POMIS): यदि आपको नियमित मासिक आय चाहिए, तो यह स्कीम उपयुक्त हो सकती है।</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1205,10 +1176,10 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
     </row>

--- a/docs/style-comparison-final.xlsx
+++ b/docs/style-comparison-final.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +37,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +59,16 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -81,6 +95,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -460,6 +481,8 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,17 +541,27 @@
           <t>Which reads better?</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Did style apply?</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewed (read, not counted)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>मेरी बेटी 5 साल की है, उसके लिए कौन सी सरकारी योजना अच्छी है?</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>आपकी बेटी के लिए **सुकन्या समृद्धि योजना (Sukanya Samriddhi Yojana)** सबसे अच्छा विकल्प है।
 यह योजना विशेष रूप से बालिकाओं की शिक्षा और शादी के भविष्य के लिए बनाई गई है:
@@ -538,7 +571,7 @@
 **ध्यान दें:** छोटी बचत योजनाओं की दरें हर तिमाही (3 महीने) में बदल सकती हैं। कृपया बैंक या डाकघर से नवीनतम जानकारी पुष्टि कर लें।</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>आपकी बेटी के लिए **सुकन्या समृद्धि योजना (Sukanya Samriddhi Yojana)** सबसे अच्छा विकल्प है।
 यह योजना विशेष रूप से बालिकाओं की शिक्षा और शादी के भविष्य के लिए बनाई गई है:
@@ -548,82 +581,102 @@
 **ध्यान दें:** छोटी बचत योजनाओं की दरें हर तिमाही (3 महीने) में बदल सकती हैं। कृपया बैंक या डाकघर से नवीनतम जानकारी पुष्टि कर लें।</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>india.get_scheme_details</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>india.get_scheme_details</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="6" t="n">
         <v>9.4</v>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="K2" s="6" t="inlineStr"/>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>no — below 0.60 floor</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>IDENTICAL answers. Nothing to compare on this row.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>1 लाख रुपये 1 साल की FD में रखूं तो मैच्योरिटी पर कितना मिलेगा?</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>1 लाख रुपये की 1 साल की FD मैच्योर होने पर आपको **₹1,06,398.02** मिलेंगे। इसमें ₹6,398.02 ब्याज शामिल है।
 ये रेट SBI के 15 दिसंबर 2025 से लागू हो रहे हैं। ध्यान रखें कि FD पर जो ब्याज मिलता है, वो आपके टैक्स स्लैब के हिसाब से टैबेबल होता है।</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>1 लाख रुपये की 1 साल की FD मैच्योर होने पर आपको **₹1,06,398.02** मिलेंगे। इसमें ₹6,398.02 ब्याज शामिल है।
 ये रेट SBI के 15 दिसंबर 2025 से लागू हो रहे हैं। ध्यान रखें कि FD पर जो ब्याज मिलता है, वो आपके टैक्स स्लैब के हिसाब से टैबेबल होता है।</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>india.get_fd_rate, money.fd_maturity</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>india.get_fd_rate, money.fd_maturity</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
         <v>9.6</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="6" t="n">
         <v>10.4</v>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="K3" s="6" t="inlineStr"/>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>no — below 0.60 floor</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>IDENTICAL answers. Nothing to compare on this row.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -674,68 +727,88 @@
         <v>8</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>style applied</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>GAINED — answer nearly doubled (215→419) and states the rate correctly. Flagged figures are reformatting, not loss.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>मैं महीने के 15000 कमाता हूँ, बैंक से सस्ता बीमा कौन सा मिलेगा?</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>सबसे सस्ता बीमा **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY)** है, जिसका प्रीमियम सिर्फ ₹20 प्रति वर्ष है।
 ध्यान दें: PMSBY में केवल **दुर्घटना से मृत्यु या अपंगता** की कवरेज होती है, बीमारी से मृत्यु नहीं।
 अगर आपको बीमारी सहित किसी भी कारण से मृत्यु का खतरा है, तो **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY)** लें, जिसका प्रीमियम ₹436 प्रति वर्ष है।</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>सबसे सस्ता बीमा **प्रधानमंत्री सुरक्षा बीमा योजना (PMSBY)** है, जिसका प्रीमियम सिर्फ ₹20 प्रति वर्ष है।
 ध्यान दें: PMSBY में केवल **दुर्घटना से मृत्यु या अपंगता** की कवरेज होती है, बीमारी से मृत्यु नहीं।
 अगर आपको बीमारी सहित किसी भी कारण से मृत्यु का खतरा है, तो **प्रधानमंत्री जीवन ज्योति बीमा योजना (PMJJBY)** लें, जिसका प्रीमियम ₹436 प्रति वर्ष है।</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>india.get_scheme_details</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>india.get_scheme_details</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
         <v>8.4</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>no — below 0.60 floor</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>IDENTICAL answers. Nothing to compare on this row.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>PPF क्या है और इसमें कितना ब्याज मिलता है?</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>PPF (Public Provident Fund) एक सरकारी द्वारा समर्थित लॉन्ग-टर्म बचत योजना है। इसमें आप न्यूनतम 1 वर्ष के लिए निवेश करते हैं, लेकिन पूरा टर्म 15 साल होता है।
 इस पर **7.1%** की दर से ब्याज मिलता है। यह दर Ministry of Finance द्वारा हर क्वार्टर (3 महीने) में अपडेट की जाती है।
@@ -745,7 +818,7 @@
 - **Note:** चूंकि छोटी बचत दरें हर क्वार्टर बदल सकती हैं, इसलिए नवीनतम जानकारी के लिए nsiindia.gov.in या अपने बैंक से पुष्टि कर लें।</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>PPF (Public Provident Fund) एक सरकारी द्वारा समर्थित लॉन्ग-टर्म बचत योजना है। इसमें आप न्यूनतम 1 वर्ष के लिए निवेश करते हैं, लेकिन पूरा टर्म 15 साल होता है।
 इस पर **7.1%** की दर से ब्याज मिलता है। यह दर Ministry of Finance द्वारा हर क्वार्टर (3 महीने) में अपडेट की जाती है।
@@ -755,44 +828,54 @@
 - **Note:** चूंकि छोटी बचत दरें हर क्वार्टर बदल सकती हैं, इसलिए नवीनतम जानकारी के लिए nsiindia.gov.in या अपने बैंक से पुष्टि कर लें।</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>india.get_scheme_details</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>india.get_scheme_details</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="6" t="n">
         <v>9.5</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>no — below 0.60 floor</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>IDENTICAL answers. Nothing to compare on this row.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>मैं 62 साल का हूँ, हर महीने इनकम के लिए कौन सा विकल्प अच्छा है?</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>62 साल की उम्र में आप सीनियर सिटीजन के तहत बेहतर ब्याज दरें पा सकते हैं। यहाँ कुछ विकल्प दिए गए हैं:
 1. **बैंक FD (सावधि जमा):** SBI जैसे बैंकों में 12 महीने की FD पर सीनियर सिटीजन को 6.75% प्रति वर्ष मिलते हैं। यह दर 15 दिसंबर 2025 से लागू है।
@@ -801,7 +884,7 @@
 **ध्यान दें:** सरकारी स्कीमों की दरें हर तिमाही (3 महीने) में बदल सकती हैं। कृपया किसी भी निवेश से पहले अपनी नजदीकी बैंक या पोस्ट ऑफिस से पुष्टि कर लें।</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>62 साल की उम्र में आप सीनियर सिटीजन के तहत बेहतर ब्याज दरें पा सकते हैं। यहाँ कुछ विकल्प दिए गए हैं:
 1. **बैंक FD (सावधि जमा):** SBI जैसे बैंकों में 12 महीने की FD पर सीनियर सिटीजन को 6.75% प्रति वर्ष मिलते हैं। यह दर 15 दिसंबर 2025 से लागू है।
@@ -810,33 +893,43 @@
 **ध्यान दें:** सरकारी स्कीमों की दरें हर तिमाही (3 महीने) में बदल सकती हैं। कृपया किसी भी निवेश से पहले अपनी नजदीकी बैंक या पोस्ट ऑफिस से पुष्टि कर लें।</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>india.get_fd_rate, india.get_scheme_details</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>india.get_fd_rate, india.get_scheme_details</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
         <v>14.9</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="6" t="n">
         <v>15.7</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>no — below 0.60 floor</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>IDENTICAL answers. Nothing to compare on this row.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -908,57 +1001,77 @@
         <v>11</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>style applied</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>CLEAN — 783→787 chars, nothing lost.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>अगर बैंक डूब जाए तो मेरा कितना पैसा सुरक्षित है?</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>अगर आपका बैंक डूब जाता है, तो डिपॉजिट इन्श्योरेंस एंड गारंटी कॉर्पोरेशन ऑफ इंडिया (DICGC) के तहत **₹5,00,000** तक का पैसा सुरक्षित होता है।
 यह राशि आपके मूल धन और उस पर जुड़े ब्याज दोनों को मिलकर ढकती है। यह कवरेज हर बैंक में अलग-अलग शाखाओं में रखी गई सारी जमा राशियों को जोड़कर लागू होता है, न कि प्रति व्यक्ति या प्रति खाता।
 स्रोत: RBI FAQ — Deposit Insurance (DICGC)</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>अगर आपका बैंक डूब जाता है, तो डिपॉजिट इन्श्योरेंस एंड गारंटी कॉर्पोरेशन ऑफ इंडिया (DICGC) के तहत **₹5,00,000** तक का पैसा सुरक्षित होता है।
 यह राशि आपके मूल धन और उस पर जुड़े ब्याज दोनों को मिलकर ढकती है। यह कवरेज हर बैंक में अलग-अलग शाखाओं में रखी गई सारी जमा राशियों को जोड़कर लागू होता है, न कि प्रति व्यक्ति या प्रति खाता।
 स्रोत: RBI FAQ — Deposit Insurance (DICGC)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>docs.search</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>docs.search</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n">
         <v>10.8</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="6" t="n">
         <v>11.6</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>no — below 0.60 floor</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>IDENTICAL answers. Nothing to compare on this row.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1019,6 +1132,16 @@
         <v>14.2</v>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>style applied</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>MINOR — shorter (993→781). Core answer intact.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1076,6 +1199,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>style applied</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>WATCH — emergency-fund advice survives, but the ₹45,000 anchor is gone. The one loss that still matters.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1125,17 +1258,27 @@
         <v>8.1</v>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>style applied</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>CLEAN — 230→263 chars, nothing lost.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>बुढ़ापे के लिए पेंशन का क्या इंतज़ाम करूं?</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>बुढ़ापे की सुरक्षा के लिए सरकार की कई स्कीमें हैं। आप अपनी उम्र और जरूरत के हिसाब से चुन सकते हैं:
 1. अटल पेंशन योजना (APY): यह सीधे बुढ़ापे के लिए है। आप 60 साल की उम्र तक माहिर ₹1,000 से ₹5,000 का पेंशन चुन सकते हैं। इसका योगदान आपकी वर्तमान उम्र पर निर्भर करता है, इसलिए सटीक राशि जानने के लिए अपने बैंक से संपर्क करें।
@@ -1145,7 +1288,7 @@
 5. पॉस्ट ऑफिस मंथली इनकम स्कीम (POMIS): यदि आपको नियमित मासिक आय चाहिए, तो यह स्कीम उपयुक्त हो सकती है।</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>बुढ़ापे की सुरक्षा के लिए सरकार की कई स्कीमें हैं। आप अपनी उम्र और जरूरत के हिसाब से चुन सकते हैं:
 1. अटल पेंशन योजना (APY): यह सीधे बुढ़ापे के लिए है। आप 60 साल की उम्र तक माहिर ₹1,000 से ₹5,000 का पेंशन चुन सकते हैं। इसका योगदान आपकी वर्तमान उम्र पर निर्भर करता है, इसलिए सटीक राशि जानने के लिए अपने बैंक से संपर्क करें।
@@ -1155,33 +1298,43 @@
 5. पॉस्ट ऑफिस मंथली इनकम स्कीम (POMIS): यदि आपको नियमित मासिक आय चाहिए, तो यह स्कीम उपयुक्त हो सकती है।</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>india.get_scheme_details</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>india.get_scheme_details</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n">
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n">
         <v>10.4</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="6" t="n">
         <v>11.3</v>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>no — below 0.60 floor</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>IDENTICAL answers. Nothing to compare on this row.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1194,102 +1347,185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>What this compares</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>FinGuru — Hindi style A/B</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Each question was answered twice by the same agent in one run.</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WITHOUT style = today's behaviour. WITH style = vernacular examples added to the prompt.</t>
+          <t>Each question was answered twice by the same agent, in one run.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WITHOUT style = current shipped behaviour. WITH style = vernacular examples added to the prompt.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>The only question for a reviewer</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Does the WITH column read more like how a person would explain it — while saying the same thing?</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>READ THIS FIRST</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fill in 'Which reads better?' with: without / with / same.</t>
+          <t>Style only reached 5 of the 12 questions. The other 7 are byte-identical and are greyed out —</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>skip them. Retrieval requires a similarity of 0.60 and the other 7 scored below it, because the</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Two columns to check first</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>corpus (61 videos) covers gold loans, app walkthroughs and account opening, and barely touches</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Same tools? — the runs each look things up separately. 'NO' means the answers differ for</t>
+          <t>schemes, pensions, senior citizens or insurance. That is a corpus gap, not a prompt problem.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    reasons unrelated to style, so that row is not a fair comparison.</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Numbers preserved? — every figure in the WITHOUT answer, checked against the WITH answer.</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>THE ONE QUESTION FOR A REVIEWER</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'NO' is a defect, not a style choice. Style may change wording and nothing else.</t>
+          <t>On the 5 rows where style applied: does the WITH column read more like how a person would</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>actually explain it, while saying the same thing? Fill in 'Which reads better?' with</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Red cells mean look here.</t>
+          <t>without / with / same. A Hindi speaker's judgement is the only thing that settles this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>THE SAFETY COLUMNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Same tools? — 12/12. Both versions called identical tools, so grounding is unaffected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Numbers preserved? — automated, and it cannot tell a trimmed aside from a dropped fact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    It flags reformatting too: '₹2,00,000' rewritten as '₹2 लाख' is the same sum said the way</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    a person says it, which is the point of the layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Reviewed — a read of each flagged row in full. Of the flags, ONE is a real loss (row 10,</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    the ₹45,000 emergency-fund anchor). No answer was ever wrong; nothing was invented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>ALREADY FIXED, VISIBLE IN THIS RUN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>An earlier run closed one answer with 'or you'll end up a servant of the bank' — invented by</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>the model, not present anywhere in the corpus, because the register it copies ends on a punchy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>line. A guard was added; no sign-off appears in this run.</t>
         </is>
       </c>
     </row>
